--- a/data/trending_integrated_20261028_10.xlsx
+++ b/data/trending_integrated_20261028_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z13"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>나무가</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19960</v>
+        <v>3795</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+16.79%</t>
+          <t>'+17.49%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.61</v>
+        <v>-0.19</v>
       </c>
       <c r="E2" t="n">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="F2" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>198</v>
+        <v>89</v>
       </c>
       <c r="H2" t="n">
-        <v>4.74</v>
+        <v>1.2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,51 +595,51 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>17090</v>
+        <v>3230</v>
       </c>
       <c r="K2" t="n">
-        <v>19270</v>
+        <v>3600</v>
       </c>
       <c r="L2" t="n">
-        <v>20000</v>
+        <v>3990</v>
       </c>
       <c r="M2" t="n">
-        <v>18070</v>
+        <v>3580</v>
       </c>
       <c r="N2" t="n">
-        <v>4.13</v>
+        <v>1.39</v>
       </c>
       <c r="O2" t="n">
-        <v>24704705860</v>
+        <v>72754189533</v>
       </c>
       <c r="P2" t="n">
-        <v>28600</v>
+        <v>8100</v>
       </c>
       <c r="Q2" t="n">
-        <v>11050</v>
+        <v>592</v>
       </c>
       <c r="R2" t="n">
-        <v>-83000</v>
+        <v>44000</v>
       </c>
       <c r="S2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>로봇 사업 확장 및 아틀라스 공급망 대장으로서의 입지 강화. 삼성, 구글, 현대차 등과의 연관성 및 높은 이익률 기반 상승 전망.</t>
+          <t>미국 광통신주 급등에 따른 동반 상승 기대감. 단기 급등 후 변동성 확대 가능성 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['로봇', '아틀라스', '공급망']</t>
+          <t>['광통신', '급등', '변동성']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>190510</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>나무가</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3705</v>
+        <v>19570</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+14.71%</t>
+          <t>'+14.51%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.19</v>
+        <v>0.61</v>
       </c>
       <c r="E3" t="n">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="F3" t="n">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="G3" t="n">
-        <v>87</v>
+        <v>214</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2</v>
+        <v>4.74</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,51 +687,51 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>3230</v>
+        <v>17090</v>
       </c>
       <c r="K3" t="n">
-        <v>3600</v>
+        <v>19270</v>
       </c>
       <c r="L3" t="n">
-        <v>3990</v>
+        <v>20450</v>
       </c>
       <c r="M3" t="n">
-        <v>3580</v>
+        <v>18070</v>
       </c>
       <c r="N3" t="n">
-        <v>1.39</v>
+        <v>4.13</v>
       </c>
       <c r="O3" t="n">
-        <v>67902973177</v>
+        <v>30137934530</v>
       </c>
       <c r="P3" t="n">
-        <v>8100</v>
+        <v>28600</v>
       </c>
       <c r="Q3" t="n">
-        <v>592</v>
+        <v>11050</v>
       </c>
       <c r="R3" t="n">
-        <v>44000</v>
+        <v>-83000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 증시 광통신주 급등에 따른 기대감. 호재 발생 시 급등 가능성 언급. 단기 변동성 및 추세 주목.</t>
+          <t>미국 휴머노이드 로봇 시장 성장 및 아틀라스 1만대 발주. 삼성, 현대차 등과의 협력 기반 최고 실적 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['광통신', '호재', '급등']</t>
+          <t>['휴머노이드', '아틀라스', '로봇주']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>190510</t>
         </is>
       </c>
     </row>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>186700</v>
+        <v>185800</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+9.12%</t>
+          <t>'+8.59%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F4" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G4" t="n">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="H4" t="n">
         <v>74.90000000000001</v>
@@ -794,7 +794,7 @@
         <v>74.89</v>
       </c>
       <c r="O4" t="n">
-        <v>321702326750</v>
+        <v>341086965050</v>
       </c>
       <c r="P4" t="n">
         <v>243500</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>외국인 매수세 유입 및 우선주 소각 기대감에 따른 강한 상승세. 단기 차익 실현 및 컨퍼런스콜 이후 전망 주시.</t>
+          <t>외인 순매수세 유입 및 우선주 소각 가능성 언급. 단기적인 주가 상승 기대감.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['우선주', '소각', '외국인매수']</t>
+          <t>['우선주', '외인 매수', '자사주']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>238000</v>
+        <v>237750</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.21%</t>
+          <t>'+7.09%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.05</v>
       </c>
       <c r="E5" t="n">
-        <v>775</v>
+        <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="G5" t="n">
-        <v>3108</v>
+        <v>3044</v>
       </c>
       <c r="H5" t="n">
         <v>46.15</v>
@@ -886,7 +886,7 @@
         <v>46.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1003089364500</v>
+        <v>1103406062750</v>
       </c>
       <c r="P5" t="n">
         <v>374500</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 증시 반도체 관련주 강세와 모건스탠리의 목표가 상향 조정에 따른 기대감이 반영되었으나, 일부 부정적인 정치적 언급이 혼재되어 있다.</t>
+          <t>반도체 업황 개선 기대감 및 외신 호평에 따른 주가 상승 전망. 쌍바닥 패턴 확인.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['반도체', '바닥 확인', '목표가 상향']</t>
+          <t>['반도체', '저점 매수', '주가 전망']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1422000</v>
+        <v>1424000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.04%</t>
+          <t>'+6.19%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>494</v>
+        <v>481</v>
       </c>
       <c r="G6" t="n">
-        <v>1477</v>
+        <v>1343</v>
       </c>
       <c r="H6" t="n">
         <v>48.61</v>
@@ -969,7 +969,7 @@
         <v>1390000</v>
       </c>
       <c r="L6" t="n">
-        <v>1423000</v>
+        <v>1433000</v>
       </c>
       <c r="M6" t="n">
         <v>1358000</v>
@@ -978,7 +978,7 @@
         <v>48.66</v>
       </c>
       <c r="O6" t="n">
-        <v>1742455876000</v>
+        <v>1963102753000</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>사상 최대 실적 발표 및 대규모 주주 환원 정책에 대한 기대감. 외인 순매수 재개 및 200 돌파 목표.</t>
+          <t>내년 주주환원 확대 계획 및 높은 수익성 전망. 컨퍼런스 콜 호평 및 외인 순매수세 유입.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['실적발표', '주주환원', '외인순매수']</t>
+          <t>['주주환원', '수익성', '외인 매수']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,83 +1023,83 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NAVER</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>183700</v>
+        <v>14370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.39%</t>
+          <t>'+4.89%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>334</v>
+        <v>63</v>
       </c>
       <c r="F7" t="n">
-        <v>210</v>
+        <v>31</v>
       </c>
       <c r="G7" t="n">
-        <v>1079</v>
+        <v>154</v>
       </c>
       <c r="H7" t="n">
-        <v>35.43</v>
+        <v>2.87</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>174300</v>
+        <v>13700</v>
       </c>
       <c r="K7" t="n">
-        <v>181100</v>
+        <v>14210</v>
       </c>
       <c r="L7" t="n">
-        <v>186900</v>
+        <v>14800</v>
       </c>
       <c r="M7" t="n">
-        <v>180000</v>
+        <v>14210</v>
       </c>
       <c r="N7" t="n">
-        <v>35.49</v>
+        <v>2.82</v>
       </c>
       <c r="O7" t="n">
-        <v>68670979900</v>
+        <v>56858682390</v>
       </c>
       <c r="P7" t="n">
-        <v>304000</v>
+        <v>31500</v>
       </c>
       <c r="Q7" t="n">
-        <v>170900</v>
+        <v>1760</v>
       </c>
       <c r="R7" t="n">
-        <v>-15000</v>
+        <v>203000</v>
       </c>
       <c r="S7" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>엔비디아 3대 주주 등극 뉴스에 대한 기대감과 함께 상승 흐름이 나타나고 있으나, 거래량 대비 상승폭이 작다는 의견과 함께 매도 의견도 혼재.</t>
+          <t>루멘텀, 코히어런트 급등에 따른 광통신 섹터 상승 기대. 외인 프로그램 매수세 유입 및 거래량 증가 요구.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['엔비디아', '주주', '거래량']</t>
+          <t>['광통신', '외국인 매수', '거래량']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>035420</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14290</v>
+        <v>2275</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.31%</t>
+          <t>'+4.84%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.05</v>
+        <v>0.18</v>
       </c>
       <c r="E8" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="F8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G8" t="n">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="H8" t="n">
-        <v>2.87</v>
+        <v>5.07</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,47 +1147,47 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>13700</v>
+        <v>2170</v>
       </c>
       <c r="K8" t="n">
-        <v>14210</v>
+        <v>2160</v>
       </c>
       <c r="L8" t="n">
-        <v>14800</v>
+        <v>2475</v>
       </c>
       <c r="M8" t="n">
-        <v>14210</v>
+        <v>2155</v>
       </c>
       <c r="N8" t="n">
-        <v>2.82</v>
+        <v>4.89</v>
       </c>
       <c r="O8" t="n">
-        <v>55556564970</v>
+        <v>34822433835</v>
       </c>
       <c r="P8" t="n">
-        <v>31500</v>
+        <v>4980</v>
       </c>
       <c r="Q8" t="n">
-        <v>1760</v>
+        <v>774</v>
       </c>
       <c r="R8" t="n">
-        <v>203000</v>
+        <v>410000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>외인 프로그램 매수세 유입 및 광통신 섹터 강세에 따른 상승 기대. 3분기 실적 발표 및 대세 상승 전망.</t>
+          <t>로봇 섹터 강세 속 앤로보틱스 주가 상승 기대감. 신용 증가 및 삼성 로봇 테마 대장주 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['외인매수', '광통신', '실적발표']</t>
+          <t>['로봇 섹터', '신용 증가', '대장주']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>NAVER</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30450</v>
+        <v>182700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.22%</t>
+          <t>'+4.82%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>46</v>
+        <v>359</v>
       </c>
       <c r="F9" t="n">
-        <v>41</v>
+        <v>221</v>
       </c>
       <c r="G9" t="n">
-        <v>175</v>
+        <v>1115</v>
       </c>
       <c r="H9" t="n">
-        <v>28.81</v>
+        <v>35.43</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,47 +1239,47 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>29500</v>
+        <v>174300</v>
       </c>
       <c r="K9" t="n">
-        <v>29900</v>
+        <v>181100</v>
       </c>
       <c r="L9" t="n">
-        <v>30650</v>
+        <v>186900</v>
       </c>
       <c r="M9" t="n">
-        <v>29900</v>
+        <v>180000</v>
       </c>
       <c r="N9" t="n">
-        <v>28.82</v>
+        <v>35.49</v>
       </c>
       <c r="O9" t="n">
-        <v>16976399525</v>
+        <v>75111603250</v>
       </c>
       <c r="P9" t="n">
-        <v>69700</v>
+        <v>304000</v>
       </c>
       <c r="Q9" t="n">
-        <v>29200</v>
+        <v>170900</v>
       </c>
       <c r="R9" t="n">
-        <v>132000</v>
+        <v>-15000</v>
       </c>
       <c r="S9" t="n">
-        <v>30000</v>
+        <v>4000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>주가 하락세 지속 및 공매도에 대한 불만. 네이버와의 비교 및 적정 주가 논란. 거래량 부재 시 추가 하락 전망.</t>
+          <t>엔비디아의 최대 주주 부상 및 야간선물 상승. 대규모 호재 대비 주가 상승폭 미미 지적.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['주가하락', '공매도', '적정주가']</t>
+          <t>['엔비디아', '최대 주주', '야간선물']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>035720</t>
+          <t>035420</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>63300</v>
+        <v>64000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+1.77%</t>
+          <t>'+2.89%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.57</v>
       </c>
       <c r="E10" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F10" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G10" t="n">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="H10" t="n">
         <v>41.01</v>
@@ -1337,7 +1337,7 @@
         <v>63000</v>
       </c>
       <c r="L10" t="n">
-        <v>63900</v>
+        <v>64000</v>
       </c>
       <c r="M10" t="n">
         <v>62200</v>
@@ -1346,7 +1346,7 @@
         <v>40.44</v>
       </c>
       <c r="O10" t="n">
-        <v>87906016900</v>
+        <v>94833514750</v>
       </c>
       <c r="P10" t="n">
         <v>67300</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>최근 코스피 수익률 1위 달성 및 자사주 매입 기대감. 중동 전쟁 종전 기대감과 함께 상승 추세 전망. 프로그램 매수세 유입 확인.</t>
+          <t>중동 전쟁 종식 기대감 및 코스피 수익률 상위에 따른 주가 상승세 지속 전망. 수광산 관련 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['수익률1위', '자사주매입', '전쟁종전']</t>
+          <t>['전쟁 종식', '코스피', '수광산']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14250</v>
+        <v>30300</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.38%</t>
+          <t>'+2.71%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.19</v>
+        <v>-0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="F11" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G11" t="n">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="H11" t="n">
-        <v>9.83</v>
+        <v>28.81</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>14450</v>
+        <v>29500</v>
       </c>
       <c r="K11" t="n">
-        <v>14750</v>
+        <v>29900</v>
       </c>
       <c r="L11" t="n">
-        <v>14870</v>
+        <v>30650</v>
       </c>
       <c r="M11" t="n">
-        <v>14250</v>
+        <v>29900</v>
       </c>
       <c r="N11" t="n">
-        <v>10.02</v>
+        <v>28.82</v>
       </c>
       <c r="O11" t="n">
-        <v>21837823110</v>
+        <v>17863005425</v>
       </c>
       <c r="P11" t="n">
-        <v>40350</v>
+        <v>69700</v>
       </c>
       <c r="Q11" t="n">
-        <v>3320</v>
+        <v>29200</v>
       </c>
       <c r="R11" t="n">
-        <v>-313000</v>
+        <v>132000</v>
       </c>
       <c r="S11" t="n">
-        <v>-31000</v>
+        <v>30000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>공매도 및 외인 매도에 대한 강한 불만 표출. 회사의 주가 관리 및 실적에 대한 부정적 인식. 일부에서는 긍정적인 전망 제시.</t>
+          <t>주가 하락 지속 및 공매도에 대한 불만. 네이버와의 비교 및 적정 주가에 대한 부정적 의견.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['공매도', '외인매도', '주가관리']</t>
+          <t>['주가 하락', '공매도', '적정 주가']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>035720</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>한화오션</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>52000</v>
+        <v>16140</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.89%</t>
+          <t>'+1.96%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.03</v>
+        <v>1.02</v>
       </c>
       <c r="E12" t="n">
-        <v>175</v>
+        <v>40</v>
       </c>
       <c r="F12" t="n">
-        <v>125</v>
+        <v>30</v>
       </c>
       <c r="G12" t="n">
-        <v>545</v>
+        <v>71</v>
       </c>
       <c r="H12" t="n">
-        <v>10.31</v>
+        <v>1.11</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>53000</v>
+        <v>15830</v>
       </c>
       <c r="K12" t="n">
-        <v>53400</v>
+        <v>17170</v>
       </c>
       <c r="L12" t="n">
-        <v>53800</v>
+        <v>17300</v>
       </c>
       <c r="M12" t="n">
-        <v>51200</v>
+        <v>15890</v>
       </c>
       <c r="N12" t="n">
-        <v>10.34</v>
+        <v>0.09</v>
       </c>
       <c r="O12" t="n">
-        <v>34749757000</v>
+        <v>69578382430</v>
       </c>
       <c r="P12" t="n">
-        <v>154800</v>
+        <v>28800</v>
       </c>
       <c r="Q12" t="n">
-        <v>51200</v>
+        <v>11550</v>
       </c>
       <c r="R12" t="n">
-        <v>-308000</v>
+        <v>-78000</v>
       </c>
       <c r="S12" t="n">
-        <v>-22000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>매출 증가에도 불구하고 주가는 하락세. 외인 및 프로그램 매도, 공매도에 대한 불만. 악재 지속 및 신저가 행진.</t>
+          <t>AI 데이터센터 방열 시스템 594억 공급 계약 체결. 삼성, 하이닉스 관련 반도체 수급 이동 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['매출증가', '주가하락', '외인매도']</t>
+          <t>['공급 계약', '데이터센터', '반도체']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>042660</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK증권</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1986</v>
+        <v>16380</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-4.75%</t>
+          <t>'-0.06%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.39</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F13" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G13" t="n">
-        <v>52</v>
+        <v>110</v>
       </c>
       <c r="H13" t="n">
-        <v>2.52</v>
+        <v>28.03</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>2085</v>
+        <v>16390</v>
       </c>
       <c r="K13" t="n">
-        <v>2005</v>
+        <v>16630</v>
       </c>
       <c r="L13" t="n">
-        <v>2010</v>
+        <v>16760</v>
       </c>
       <c r="M13" t="n">
-        <v>1805</v>
+        <v>16360</v>
       </c>
       <c r="N13" t="n">
-        <v>2.13</v>
+        <v>27.96</v>
       </c>
       <c r="O13" t="n">
-        <v>10503765643</v>
+        <v>16282559350</v>
       </c>
       <c r="P13" t="n">
-        <v>6190</v>
+        <v>35350</v>
       </c>
       <c r="Q13" t="n">
-        <v>636</v>
+        <v>16270</v>
       </c>
       <c r="R13" t="n">
-        <v>-601000</v>
+        <v>-103000</v>
       </c>
       <c r="S13" t="n">
-        <v>19000</v>
+        <v>-30000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>액면 병합 이후 주가 하락에 대한 개인 투자자들의 불만과 원인 분석 시도. 일부에서는 추매 의견도 존재.</t>
+          <t>주가 하락 및 목표 주가 하향 조정에 대한 불만. 조선업 전망에 대한 부정적 시각.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,18 +1647,294 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['액면병합', '개인투자자', '추매']</t>
+          <t>['목표 주가', '조선업', '주가 하락']</t>
         </is>
       </c>
       <c r="X13" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>010140</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>14350</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>'-0.69%</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="E14" t="n">
+        <v>97</v>
+      </c>
+      <c r="F14" t="n">
+        <v>58</v>
+      </c>
+      <c r="G14" t="n">
+        <v>179</v>
+      </c>
+      <c r="H14" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>14450</v>
+      </c>
+      <c r="K14" t="n">
+        <v>14750</v>
+      </c>
+      <c r="L14" t="n">
+        <v>14870</v>
+      </c>
+      <c r="M14" t="n">
+        <v>14240</v>
+      </c>
+      <c r="N14" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="O14" t="n">
+        <v>23719146815</v>
+      </c>
+      <c r="P14" t="n">
+        <v>40350</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3320</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-313000</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-31000</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>주가 하락 및 공매도에 대한 불만 표출. 목표가 하향 조정에 대한 부정적 의견.</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>['공매도', '주가 하락', '개잡주']</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>한화오션</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>51900</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>'-2.08%</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="E15" t="n">
+        <v>200</v>
+      </c>
+      <c r="F15" t="n">
+        <v>135</v>
+      </c>
+      <c r="G15" t="n">
+        <v>574</v>
+      </c>
+      <c r="H15" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>53000</v>
+      </c>
+      <c r="K15" t="n">
+        <v>53400</v>
+      </c>
+      <c r="L15" t="n">
+        <v>53800</v>
+      </c>
+      <c r="M15" t="n">
+        <v>51200</v>
+      </c>
+      <c r="N15" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="O15" t="n">
+        <v>37047638050</v>
+      </c>
+      <c r="P15" t="n">
+        <v>154800</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>51200</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-308000</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-22000</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>주가 하락 및 공매도에 대한 불만 표출. 실적 개선에도 불구하고 주가 부진에 대한 비판.</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>['공매도', '주가 하락', '실적 부진']</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
         <v>1</v>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>042660</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SK증권</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1981</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>'-4.99%</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E16" t="n">
+        <v>55</v>
+      </c>
+      <c r="F16" t="n">
+        <v>40</v>
+      </c>
+      <c r="G16" t="n">
+        <v>63</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>2085</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2005</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2010</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1805</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="O16" t="n">
+        <v>10851148722</v>
+      </c>
+      <c r="P16" t="n">
+        <v>6190</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>636</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-601000</v>
+      </c>
+      <c r="S16" t="n">
+        <v>19000</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>액면병합 관련 논의 및 주가 하락에 대한 의문 제기. 일부 투자자는 추가 매수를 계획.</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>['액면병합', '주가 하락', '개인 투자자']</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
         <is>
           <t>001510</t>
         </is>

--- a/data/trending_integrated_20261028_10.xlsx
+++ b/data/trending_integrated_20261028_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z16"/>
+  <dimension ref="A1:Z19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3795</v>
+        <v>29600</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+17.49%</t>
+          <t>'+24.63%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.19</v>
+        <v>-0.15</v>
       </c>
       <c r="E2" t="n">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="F2" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="G2" t="n">
-        <v>89</v>
+        <v>115</v>
       </c>
       <c r="H2" t="n">
-        <v>1.2</v>
+        <v>5.16</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,47 +595,47 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>3230</v>
+        <v>23750</v>
       </c>
       <c r="K2" t="n">
-        <v>3600</v>
+        <v>24200</v>
       </c>
       <c r="L2" t="n">
-        <v>3990</v>
+        <v>29900</v>
       </c>
       <c r="M2" t="n">
-        <v>3580</v>
+        <v>24200</v>
       </c>
       <c r="N2" t="n">
-        <v>1.39</v>
+        <v>5.31</v>
       </c>
       <c r="O2" t="n">
-        <v>72754189533</v>
+        <v>110471572525</v>
       </c>
       <c r="P2" t="n">
-        <v>8100</v>
+        <v>50600</v>
       </c>
       <c r="Q2" t="n">
-        <v>592</v>
+        <v>13210</v>
       </c>
       <c r="R2" t="n">
-        <v>44000</v>
+        <v>-15000</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등에 따른 동반 상승 기대감. 단기 급등 후 변동성 확대 가능성 언급.</t>
+          <t>삼성의 지분 투자 가능성 및 로봇 관련 행사 참여 기대감에 따른 주가 상승 전망. 이재용 회장 관련 언급과 품절주 특성 부각.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['광통신', '급등', '변동성']</t>
+          <t>['삼성 투자', '로봇 섹터', '품절주']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>나무가</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19570</v>
+        <v>3785</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+14.51%</t>
+          <t>'+17.18%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.61</v>
+        <v>-0.19</v>
       </c>
       <c r="E3" t="n">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="F3" t="n">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>214</v>
+        <v>95</v>
       </c>
       <c r="H3" t="n">
-        <v>4.74</v>
+        <v>1.2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,51 +687,51 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>17090</v>
+        <v>3230</v>
       </c>
       <c r="K3" t="n">
-        <v>19270</v>
+        <v>3600</v>
       </c>
       <c r="L3" t="n">
-        <v>20450</v>
+        <v>3990</v>
       </c>
       <c r="M3" t="n">
-        <v>18070</v>
+        <v>3580</v>
       </c>
       <c r="N3" t="n">
-        <v>4.13</v>
+        <v>1.39</v>
       </c>
       <c r="O3" t="n">
-        <v>30137934530</v>
+        <v>77263604241</v>
       </c>
       <c r="P3" t="n">
-        <v>28600</v>
+        <v>8100</v>
       </c>
       <c r="Q3" t="n">
-        <v>11050</v>
+        <v>592</v>
       </c>
       <c r="R3" t="n">
-        <v>-83000</v>
+        <v>44000</v>
       </c>
       <c r="S3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 휴머노이드 로봇 시장 성장 및 아틀라스 1만대 발주. 삼성, 현대차 등과의 협력 기반 최고 실적 전망.</t>
+          <t>미국 광통신주 강세 및 갭 상승 출발, 단기 급등락 후 재상승 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['휴머노이드', '아틀라스', '로봇주']</t>
+          <t>['빛과전자', '광통신', '갭상승']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,90 +740,90 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>190510</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>나무가</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>185800</v>
+        <v>19240</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+8.59%</t>
+          <t>'+12.58%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.01</v>
+        <v>0.61</v>
       </c>
       <c r="E4" t="n">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="F4" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="G4" t="n">
-        <v>136</v>
+        <v>255</v>
       </c>
       <c r="H4" t="n">
-        <v>74.90000000000001</v>
+        <v>4.74</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>171100</v>
+        <v>17090</v>
       </c>
       <c r="K4" t="n">
-        <v>176300</v>
+        <v>19270</v>
       </c>
       <c r="L4" t="n">
-        <v>187400</v>
+        <v>20450</v>
       </c>
       <c r="M4" t="n">
-        <v>175400</v>
+        <v>18070</v>
       </c>
       <c r="N4" t="n">
-        <v>74.89</v>
+        <v>4.13</v>
       </c>
       <c r="O4" t="n">
-        <v>341086965050</v>
+        <v>32837254990</v>
       </c>
       <c r="P4" t="n">
-        <v>243500</v>
+        <v>28600</v>
       </c>
       <c r="Q4" t="n">
-        <v>71000</v>
+        <v>11050</v>
       </c>
       <c r="R4" t="n">
-        <v>314000</v>
+        <v>-83000</v>
       </c>
       <c r="S4" t="n">
-        <v>-22000</v>
+        <v>1000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>외인 순매수세 유입 및 우선주 소각 가능성 언급. 단기적인 주가 상승 기대감.</t>
+          <t>아틀라스 로봇 발주 및 현대차의 로봇 도입 소식에 따른 로봇 섹터 내 나무가 부각. 삼성, 아틀라스 공급망 대장으로서의 이익 규모 및 타사 대비 경쟁력 강조.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['우선주', '외인 매수', '자사주']</t>
+          <t>['로봇 섹터', '아틀라스 공급', '이익 규모']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,77 +832,77 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>190510</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>237750</v>
+        <v>2680</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.09%</t>
+          <t>'+9.39%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.05</v>
+        <v>0.68</v>
       </c>
       <c r="E5" t="n">
-        <v>800</v>
+        <v>45</v>
       </c>
       <c r="F5" t="n">
-        <v>423</v>
+        <v>33</v>
       </c>
       <c r="G5" t="n">
-        <v>3044</v>
+        <v>44</v>
       </c>
       <c r="H5" t="n">
-        <v>46.15</v>
+        <v>1.69</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>222000</v>
+        <v>2450</v>
       </c>
       <c r="K5" t="n">
-        <v>231000</v>
+        <v>2525</v>
       </c>
       <c r="L5" t="n">
-        <v>239000</v>
+        <v>2965</v>
       </c>
       <c r="M5" t="n">
-        <v>228000</v>
+        <v>2505</v>
       </c>
       <c r="N5" t="n">
-        <v>46.1</v>
+        <v>1.01</v>
       </c>
       <c r="O5" t="n">
-        <v>1103406062750</v>
+        <v>55123891316</v>
       </c>
       <c r="P5" t="n">
-        <v>374500</v>
+        <v>2965</v>
       </c>
       <c r="Q5" t="n">
-        <v>94500</v>
+        <v>865</v>
       </c>
       <c r="R5" t="n">
-        <v>539000</v>
+        <v>1002000</v>
       </c>
       <c r="S5" t="n">
-        <v>339000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>반도체 업황 개선 기대감 및 외신 호평에 따른 주가 상승 전망. 쌍바닥 패턴 확인.</t>
+          <t>미국 1000억원 규모 하이브리드 부품 수주, 개인 물량 흡수 및 3000원 돌파 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['반도체', '저점 매수', '주가 전망']</t>
+          <t>['삼기에너지솔루션즈', '수주', '하이브리드부품']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>419050</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1424000</v>
+        <v>186150</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.19%</t>
+          <t>'+8.80%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>800</v>
+        <v>55</v>
       </c>
       <c r="F6" t="n">
-        <v>481</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>1343</v>
+        <v>139</v>
       </c>
       <c r="H6" t="n">
-        <v>48.61</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1341000</v>
+        <v>171100</v>
       </c>
       <c r="K6" t="n">
-        <v>1390000</v>
+        <v>176300</v>
       </c>
       <c r="L6" t="n">
-        <v>1433000</v>
+        <v>187400</v>
       </c>
       <c r="M6" t="n">
-        <v>1358000</v>
+        <v>175400</v>
       </c>
       <c r="N6" t="n">
-        <v>48.66</v>
+        <v>74.89</v>
       </c>
       <c r="O6" t="n">
-        <v>1963102753000</v>
+        <v>360999686150</v>
       </c>
       <c r="P6" t="n">
-        <v>2987000</v>
+        <v>243500</v>
       </c>
       <c r="Q6" t="n">
-        <v>501000</v>
+        <v>71000</v>
       </c>
       <c r="R6" t="n">
-        <v>-77000</v>
+        <v>314000</v>
       </c>
       <c r="S6" t="n">
-        <v>25000</v>
+        <v>-22000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>내년 주주환원 확대 계획 및 높은 수익성 전망. 컨퍼런스 콜 호평 및 외인 순매수세 유입.</t>
+          <t>외국인 매수세 유입 및 숏 스퀴즈 기대감, 분기배당 비교.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['주주환원', '수익성', '외인 매수']</t>
+          <t>['삼성전자우', '외국인매수', '숏스퀴즈']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,77 +1016,77 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14370</v>
+        <v>239000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.89%</t>
+          <t>'+7.66%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>63</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>31</v>
+        <v>420</v>
       </c>
       <c r="G7" t="n">
-        <v>154</v>
+        <v>2596</v>
       </c>
       <c r="H7" t="n">
-        <v>2.87</v>
+        <v>46.15</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>13700</v>
+        <v>222000</v>
       </c>
       <c r="K7" t="n">
-        <v>14210</v>
+        <v>231000</v>
       </c>
       <c r="L7" t="n">
-        <v>14800</v>
+        <v>239500</v>
       </c>
       <c r="M7" t="n">
-        <v>14210</v>
+        <v>228000</v>
       </c>
       <c r="N7" t="n">
-        <v>2.82</v>
+        <v>46.1</v>
       </c>
       <c r="O7" t="n">
-        <v>56858682390</v>
+        <v>1254644572250</v>
       </c>
       <c r="P7" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q7" t="n">
-        <v>1760</v>
+        <v>94500</v>
       </c>
       <c r="R7" t="n">
-        <v>203000</v>
+        <v>539000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>339000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>루멘텀, 코히어런트 급등에 따른 광통신 섹터 상승 기대. 외인 프로그램 매수세 유입 및 거래량 증가 요구.</t>
+          <t>이스라엘 관련 뉴스 및 AI 대체 논의 속 기대감 형성, 삼성전자 이재용 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['광통신', '외국인 매수', '거래량']</t>
+          <t>['삼성전자', 'AI', '이스라엘']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,90 +1108,90 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2275</v>
+        <v>1442000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.84%</t>
+          <t>'+7.53%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.18</v>
+        <v>-0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>41</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>29</v>
+        <v>473</v>
       </c>
       <c r="G8" t="n">
-        <v>116</v>
+        <v>1418</v>
       </c>
       <c r="H8" t="n">
-        <v>5.07</v>
+        <v>48.61</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>2170</v>
+        <v>1341000</v>
       </c>
       <c r="K8" t="n">
-        <v>2160</v>
+        <v>1390000</v>
       </c>
       <c r="L8" t="n">
-        <v>2475</v>
+        <v>1442000</v>
       </c>
       <c r="M8" t="n">
-        <v>2155</v>
+        <v>1358000</v>
       </c>
       <c r="N8" t="n">
-        <v>4.89</v>
+        <v>48.66</v>
       </c>
       <c r="O8" t="n">
-        <v>34822433835</v>
+        <v>2128175795000</v>
       </c>
       <c r="P8" t="n">
-        <v>4980</v>
+        <v>2987000</v>
       </c>
       <c r="Q8" t="n">
-        <v>774</v>
+        <v>501000</v>
       </c>
       <c r="R8" t="n">
-        <v>410000</v>
+        <v>-77000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>로봇 섹터 강세 속 앤로보틱스 주가 상승 기대감. 신용 증가 및 삼성 로봇 테마 대장주 언급.</t>
+          <t>컨퍼런스콜 호평 및 향후 100조 주주 환원 발표, 외인 순매수 재개 및 200 돌파 기대.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['로봇 섹터', '신용 증가', '대장주']</t>
+          <t>['SK하이닉스', '주주환원', '컨퍼런스콜']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NAVER</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>182700</v>
+        <v>14460</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.82%</t>
+          <t>'+5.55%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>359</v>
+        <v>66</v>
       </c>
       <c r="F9" t="n">
-        <v>221</v>
+        <v>34</v>
       </c>
       <c r="G9" t="n">
-        <v>1115</v>
+        <v>158</v>
       </c>
       <c r="H9" t="n">
-        <v>35.43</v>
+        <v>2.87</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>174300</v>
+        <v>13700</v>
       </c>
       <c r="K9" t="n">
-        <v>181100</v>
+        <v>14210</v>
       </c>
       <c r="L9" t="n">
-        <v>186900</v>
+        <v>14800</v>
       </c>
       <c r="M9" t="n">
-        <v>180000</v>
+        <v>14210</v>
       </c>
       <c r="N9" t="n">
-        <v>35.49</v>
+        <v>2.82</v>
       </c>
       <c r="O9" t="n">
-        <v>75111603250</v>
+        <v>59489907180</v>
       </c>
       <c r="P9" t="n">
-        <v>304000</v>
+        <v>31500</v>
       </c>
       <c r="Q9" t="n">
-        <v>170900</v>
+        <v>1760</v>
       </c>
       <c r="R9" t="n">
-        <v>-15000</v>
+        <v>203000</v>
       </c>
       <c r="S9" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>엔비디아의 최대 주주 부상 및 야간선물 상승. 대규모 호재 대비 주가 상승폭 미미 지적.</t>
+          <t>광통신 섹터 내에서의 주가 상승 기대감과 외국인 프로그램 매수세 유입 정황. 3분기 실적 발표 및 공매도 세력의 움직임 주목.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['엔비디아', '최대 주주', '야간선물']</t>
+          <t>['광통신', '외국인 매수', '공매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>035420</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>NAVER</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>64000</v>
+        <v>183000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.89%</t>
+          <t>'+4.99%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.57</v>
+        <v>-0.06</v>
       </c>
       <c r="E10" t="n">
-        <v>63</v>
+        <v>382</v>
       </c>
       <c r="F10" t="n">
-        <v>45</v>
+        <v>234</v>
       </c>
       <c r="G10" t="n">
-        <v>272</v>
+        <v>1163</v>
       </c>
       <c r="H10" t="n">
-        <v>41.01</v>
+        <v>35.43</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>62200</v>
+        <v>174300</v>
       </c>
       <c r="K10" t="n">
-        <v>63000</v>
+        <v>181100</v>
       </c>
       <c r="L10" t="n">
-        <v>64000</v>
+        <v>186900</v>
       </c>
       <c r="M10" t="n">
-        <v>62200</v>
+        <v>180000</v>
       </c>
       <c r="N10" t="n">
-        <v>40.44</v>
+        <v>35.49</v>
       </c>
       <c r="O10" t="n">
-        <v>94833514750</v>
+        <v>79501696750</v>
       </c>
       <c r="P10" t="n">
-        <v>67300</v>
+        <v>304000</v>
       </c>
       <c r="Q10" t="n">
-        <v>23150</v>
+        <v>170900</v>
       </c>
       <c r="R10" t="n">
-        <v>129000</v>
+        <v>-15000</v>
       </c>
       <c r="S10" t="n">
-        <v>31000</v>
+        <v>4000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>중동 전쟁 종식 기대감 및 코스피 수익률 상위에 따른 주가 상승세 지속 전망. 수광산 관련 언급.</t>
+          <t>엔비디아의 최대 주주 부상 및 야간선물 상승. 대규모 호재 대비 주가 상승폭 미미 지적.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['전쟁 종식', '코스피', '수광산']</t>
+          <t>['엔비디아', '최대 주주', '야간선물']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>035420</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>30300</v>
+        <v>2250</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.71%</t>
+          <t>'+3.69%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.01</v>
+        <v>0.18</v>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F11" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="G11" t="n">
-        <v>177</v>
+        <v>130</v>
       </c>
       <c r="H11" t="n">
-        <v>28.81</v>
+        <v>5.07</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>29500</v>
+        <v>2170</v>
       </c>
       <c r="K11" t="n">
-        <v>29900</v>
+        <v>2160</v>
       </c>
       <c r="L11" t="n">
-        <v>30650</v>
+        <v>2475</v>
       </c>
       <c r="M11" t="n">
-        <v>29900</v>
+        <v>2155</v>
       </c>
       <c r="N11" t="n">
-        <v>28.82</v>
+        <v>4.89</v>
       </c>
       <c r="O11" t="n">
-        <v>17863005425</v>
+        <v>36143231789</v>
       </c>
       <c r="P11" t="n">
-        <v>69700</v>
+        <v>4980</v>
       </c>
       <c r="Q11" t="n">
-        <v>29200</v>
+        <v>774</v>
       </c>
       <c r="R11" t="n">
-        <v>132000</v>
+        <v>410000</v>
       </c>
       <c r="S11" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>주가 하락 지속 및 공매도에 대한 불만. 네이버와의 비교 및 적정 주가에 대한 부정적 의견.</t>
+          <t>로봇 섹터 강세 속 앤로보틱스의 주가 흐름에 대한 기대와 우려 혼재. 신용 물량 증가 및 단기 매매 세력의 움직임 관찰.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['주가 하락', '공매도', '적정 주가']</t>
+          <t>['로봇 섹터', '신용 물량', '단기 매매']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>035720</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16140</v>
+        <v>8430</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+1.96%</t>
+          <t>'+2.80%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.02</v>
+        <v>0.27</v>
       </c>
       <c r="E12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G12" t="n">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="H12" t="n">
-        <v>1.11</v>
+        <v>1.42</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>15830</v>
+        <v>8200</v>
       </c>
       <c r="K12" t="n">
-        <v>17170</v>
+        <v>8230</v>
       </c>
       <c r="L12" t="n">
-        <v>17300</v>
+        <v>9050</v>
       </c>
       <c r="M12" t="n">
-        <v>15890</v>
+        <v>8100</v>
       </c>
       <c r="N12" t="n">
-        <v>0.09</v>
+        <v>1.15</v>
       </c>
       <c r="O12" t="n">
-        <v>69578382430</v>
+        <v>34257612580</v>
       </c>
       <c r="P12" t="n">
-        <v>28800</v>
+        <v>9820</v>
       </c>
       <c r="Q12" t="n">
-        <v>11550</v>
+        <v>2965</v>
       </c>
       <c r="R12" t="n">
-        <v>-78000</v>
+        <v>-11000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>AI 데이터센터 방열 시스템 594억 공급 계약 체결. 삼성, 하이닉스 관련 반도체 수급 이동 전망.</t>
+          <t>미국 양자, 보안주 급등과 국내 보안 사고 뉴스에 따른 IT 보안 섹터 관심 증대. 샌즈랩의 AI 시대 보안 역할 및 과거 보안 대장주 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['공급 계약', '데이터센터', '반도체']</t>
+          <t>['IT 보안', 'AI 시대', '해킹 사고']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16380</v>
+        <v>30300</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.06%</t>
+          <t>'+2.71%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="F13" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="G13" t="n">
-        <v>110</v>
+        <v>186</v>
       </c>
       <c r="H13" t="n">
-        <v>28.03</v>
+        <v>28.81</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>16390</v>
+        <v>29500</v>
       </c>
       <c r="K13" t="n">
-        <v>16630</v>
+        <v>29900</v>
       </c>
       <c r="L13" t="n">
-        <v>16760</v>
+        <v>30650</v>
       </c>
       <c r="M13" t="n">
-        <v>16360</v>
+        <v>29900</v>
       </c>
       <c r="N13" t="n">
-        <v>27.96</v>
+        <v>28.82</v>
       </c>
       <c r="O13" t="n">
-        <v>16282559350</v>
+        <v>18657717925</v>
       </c>
       <c r="P13" t="n">
-        <v>35350</v>
+        <v>69700</v>
       </c>
       <c r="Q13" t="n">
-        <v>16270</v>
+        <v>29200</v>
       </c>
       <c r="R13" t="n">
-        <v>-103000</v>
+        <v>132000</v>
       </c>
       <c r="S13" t="n">
-        <v>-30000</v>
+        <v>30000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>주가 하락 및 목표 주가 하향 조정에 대한 불만. 조선업 전망에 대한 부정적 시각.</t>
+          <t>매도세 지속 및 3만원 이하 예상, 네이버와 비교 및 공매도 이슈.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['목표 주가', '조선업', '주가 하락']</t>
+          <t>['카카오', '공매도', '네이버']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>035720</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14350</v>
+        <v>63600</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.69%</t>
+          <t>'+2.25%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.19</v>
+        <v>0.57</v>
       </c>
       <c r="E14" t="n">
-        <v>97</v>
+        <v>69</v>
       </c>
       <c r="F14" t="n">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="G14" t="n">
-        <v>179</v>
+        <v>301</v>
       </c>
       <c r="H14" t="n">
-        <v>9.83</v>
+        <v>41.01</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>14450</v>
+        <v>62200</v>
       </c>
       <c r="K14" t="n">
-        <v>14750</v>
+        <v>63000</v>
       </c>
       <c r="L14" t="n">
-        <v>14870</v>
+        <v>64300</v>
       </c>
       <c r="M14" t="n">
-        <v>14240</v>
+        <v>62200</v>
       </c>
       <c r="N14" t="n">
-        <v>10.02</v>
+        <v>40.44</v>
       </c>
       <c r="O14" t="n">
-        <v>23719146815</v>
+        <v>111780919050</v>
       </c>
       <c r="P14" t="n">
-        <v>40350</v>
+        <v>67300</v>
       </c>
       <c r="Q14" t="n">
-        <v>3320</v>
+        <v>23150</v>
       </c>
       <c r="R14" t="n">
-        <v>-313000</v>
+        <v>129000</v>
       </c>
       <c r="S14" t="n">
-        <v>-31000</v>
+        <v>31000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>주가 하락 및 공매도에 대한 불만 표출. 목표가 하향 조정에 대한 부정적 의견.</t>
+          <t>이란 평화 회담 기대감 속 국제유가 하락, 코스피 수익률 1위 달성 및 자사주 매입 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['공매도', '주가 하락', '개잡주']</t>
+          <t>['삼성E&amp;A', '국제유가', '자사주매입']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>한화오션</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>51900</v>
+        <v>16100</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-2.08%</t>
+          <t>'+1.71%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.03</v>
+        <v>1.02</v>
       </c>
       <c r="E15" t="n">
-        <v>200</v>
+        <v>45</v>
       </c>
       <c r="F15" t="n">
-        <v>135</v>
+        <v>34</v>
       </c>
       <c r="G15" t="n">
-        <v>574</v>
+        <v>76</v>
       </c>
       <c r="H15" t="n">
-        <v>10.31</v>
+        <v>1.11</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>53000</v>
+        <v>15830</v>
       </c>
       <c r="K15" t="n">
-        <v>53400</v>
+        <v>17170</v>
       </c>
       <c r="L15" t="n">
-        <v>53800</v>
+        <v>17300</v>
       </c>
       <c r="M15" t="n">
-        <v>51200</v>
+        <v>15830</v>
       </c>
       <c r="N15" t="n">
-        <v>10.34</v>
+        <v>0.09</v>
       </c>
       <c r="O15" t="n">
-        <v>37047638050</v>
+        <v>75269778170</v>
       </c>
       <c r="P15" t="n">
-        <v>154800</v>
+        <v>28800</v>
       </c>
       <c r="Q15" t="n">
-        <v>51200</v>
+        <v>11550</v>
       </c>
       <c r="R15" t="n">
-        <v>-308000</v>
+        <v>-78000</v>
       </c>
       <c r="S15" t="n">
-        <v>-22000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>주가 하락 및 공매도에 대한 불만 표출. 실적 개선에도 불구하고 주가 부진에 대한 비판.</t>
+          <t>AI 데이터센터 방열 시스템 공급 계약 및 삼성, 하이닉스와의 연관성을 바탕으로 한 밸류에이션 기대감. 보호예수 물량 해제와 수급 동향 주시.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['공매도', '주가 하락', '실적 부진']</t>
+          <t>['AI 데이터센터', '방열 시스템', '밸류에이션']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>042660</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SK증권</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1981</v>
+        <v>16410</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.99%</t>
+          <t>'+0.12%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.39</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F16" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G16" t="n">
-        <v>63</v>
+        <v>154</v>
       </c>
       <c r="H16" t="n">
-        <v>2.52</v>
+        <v>28.03</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,58 +1883,334 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>2085</v>
+        <v>16390</v>
       </c>
       <c r="K16" t="n">
-        <v>2005</v>
+        <v>16630</v>
       </c>
       <c r="L16" t="n">
-        <v>2010</v>
+        <v>16760</v>
       </c>
       <c r="M16" t="n">
-        <v>1805</v>
+        <v>16350</v>
       </c>
       <c r="N16" t="n">
-        <v>2.13</v>
+        <v>27.96</v>
       </c>
       <c r="O16" t="n">
-        <v>10851148722</v>
+        <v>17956045410</v>
       </c>
       <c r="P16" t="n">
-        <v>6190</v>
+        <v>35350</v>
       </c>
       <c r="Q16" t="n">
-        <v>636</v>
+        <v>16270</v>
       </c>
       <c r="R16" t="n">
-        <v>-601000</v>
+        <v>-103000</v>
       </c>
       <c r="S16" t="n">
-        <v>19000</v>
+        <v>-30000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>액면병합 관련 논의 및 주가 하락에 대한 의문 제기. 일부 투자자는 추가 매수를 계획.</t>
+          <t>외국인, 기관 프로그램 매수세 속 목표주가 하향 조정 및 신용 물량 주의보.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>['삼성중공업', '목표주가', '외국인매수']</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>010140</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>14370</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>'-0.55%</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="E17" t="n">
+        <v>105</v>
+      </c>
+      <c r="F17" t="n">
+        <v>62</v>
+      </c>
+      <c r="G17" t="n">
+        <v>187</v>
+      </c>
+      <c r="H17" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>14450</v>
+      </c>
+      <c r="K17" t="n">
+        <v>14750</v>
+      </c>
+      <c r="L17" t="n">
+        <v>14870</v>
+      </c>
+      <c r="M17" t="n">
+        <v>14240</v>
+      </c>
+      <c r="N17" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="O17" t="n">
+        <v>26081755140</v>
+      </c>
+      <c r="P17" t="n">
+        <v>40350</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3320</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-313000</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-31000</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>주가 하락 및 공매도에 대한 불만 표출. 목표가 하향 조정에 대한 부정적 의견.</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>['공매도', '주가 하락', '개잡주']</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>한화오션</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>52100</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>'-1.70%</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="E18" t="n">
+        <v>222</v>
+      </c>
+      <c r="F18" t="n">
+        <v>147</v>
+      </c>
+      <c r="G18" t="n">
+        <v>660</v>
+      </c>
+      <c r="H18" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>53000</v>
+      </c>
+      <c r="K18" t="n">
+        <v>53400</v>
+      </c>
+      <c r="L18" t="n">
+        <v>53800</v>
+      </c>
+      <c r="M18" t="n">
+        <v>51200</v>
+      </c>
+      <c r="N18" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="O18" t="n">
+        <v>39136525700</v>
+      </c>
+      <c r="P18" t="n">
+        <v>154800</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>51200</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-308000</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-22000</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>강한 지수 반등에도 하락세 지속, 외인/프로그램 폭탄 매도 관찰.</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
         <v>0.2</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>['액면병합', '주가 하락', '개인 투자자']</t>
-        </is>
-      </c>
-      <c r="X16" t="n">
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>['한화오션', '외인매도', '지수반등']</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
         <v>1</v>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>042660</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SK증권</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1986</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>'-4.75%</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E19" t="n">
+        <v>60</v>
+      </c>
+      <c r="F19" t="n">
+        <v>45</v>
+      </c>
+      <c r="G19" t="n">
+        <v>67</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>2085</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2005</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2010</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1805</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="O19" t="n">
+        <v>11230999466</v>
+      </c>
+      <c r="P19" t="n">
+        <v>6190</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>636</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-601000</v>
+      </c>
+      <c r="S19" t="n">
+        <v>19000</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>액면병합 이슈 속 개인 매도세 관찰, 긍정적 전망 언급 있으나 불확실.</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>['액면병합', '개인매도', '전망']</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
         <is>
           <t>001510</t>
         </is>

--- a/data/trending_integrated_20261028_10.xlsx
+++ b/data/trending_integrated_20261028_10.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29600</v>
+        <v>29050</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+24.63%</t>
+          <t>'+22.32%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.15</v>
       </c>
       <c r="E2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F2" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G2" t="n">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="H2" t="n">
         <v>5.16</v>
@@ -610,7 +610,7 @@
         <v>5.31</v>
       </c>
       <c r="O2" t="n">
-        <v>110471572525</v>
+        <v>116207895725</v>
       </c>
       <c r="P2" t="n">
         <v>50600</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>삼성의 지분 투자 가능성 및 로봇 관련 행사 참여 기대감에 따른 주가 상승 전망. 이재용 회장 관련 언급과 품절주 특성 부각.</t>
+          <t>원익홀딩스, 삼성 지분 투자 및 로봇 행사 관련 기대감. 이재용 회장 로봇 관련 행보 및 SK 입질 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['삼성 투자', '로봇 섹터', '품절주']</t>
+          <t>['로봇주', '삼성 투자', '이재용']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3785</v>
+        <v>3915</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.18%</t>
+          <t>'+21.21%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.19</v>
       </c>
       <c r="E3" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F3" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="H3" t="n">
         <v>1.2</v>
@@ -702,7 +702,7 @@
         <v>1.39</v>
       </c>
       <c r="O3" t="n">
-        <v>77263604241</v>
+        <v>83493241183</v>
       </c>
       <c r="P3" t="n">
         <v>8100</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 광통신주 강세 및 갭 상승 출발, 단기 급등락 후 재상승 기대.</t>
+          <t>미국 광통신주 강세와 함께 상승 기대감. 갭 상승 후 매물대 돌파 시 추가 상승 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['빛과전자', '광통신', '갭상승']</t>
+          <t>['광통신', '갭 상승', '매물대']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19240</v>
+        <v>19030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+12.58%</t>
+          <t>'+11.35%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.61</v>
       </c>
       <c r="E4" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F4" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G4" t="n">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="H4" t="n">
         <v>4.74</v>
@@ -794,7 +794,7 @@
         <v>4.13</v>
       </c>
       <c r="O4" t="n">
-        <v>32837254990</v>
+        <v>34215427790</v>
       </c>
       <c r="P4" t="n">
         <v>28600</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>아틀라스 로봇 발주 및 현대차의 로봇 도입 소식에 따른 로봇 섹터 내 나무가 부각. 삼성, 아틀라스 공급망 대장으로서의 이익 규모 및 타사 대비 경쟁력 강조.</t>
+          <t>나무가, 휴머노이드 로봇 '아틀라스' 1만대 발주 및 삼성 공급망 포함. 로봇 눈 신사업 및 VR 모듈 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['로봇 섹터', '아틀라스 공급', '이익 규모']</t>
+          <t>['휴머노이드 로봇', '아틀라스', '삼성 공급망']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2680</v>
+        <v>2675</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+9.39%</t>
+          <t>'+9.18%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.68</v>
       </c>
       <c r="E5" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G5" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="H5" t="n">
         <v>1.69</v>
@@ -886,7 +886,7 @@
         <v>1.01</v>
       </c>
       <c r="O5" t="n">
-        <v>55123891316</v>
+        <v>56874860638</v>
       </c>
       <c r="P5" t="n">
         <v>2965</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 1000억원 규모 하이브리드 부품 수주, 개인 물량 흡수 및 3000원 돌파 기대.</t>
+          <t>삼기에너지솔루션즈, 미국 1000억 규모 하이브리드 부품 수주 뉴스. 전환사채 전환 및 프로그램 매수세 유입.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['삼기에너지솔루션즈', '수주', '하이브리드부품']</t>
+          <t>['하이브리드 부품', '전환사채', '프로그램 매수']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>186150</v>
+        <v>186500</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+8.80%</t>
+          <t>'+9.00%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F6" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G6" t="n">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="H6" t="n">
         <v>74.90000000000001</v>
@@ -978,7 +978,7 @@
         <v>74.89</v>
       </c>
       <c r="O6" t="n">
-        <v>360999686150</v>
+        <v>387819617500</v>
       </c>
       <c r="P6" t="n">
         <v>243500</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>외국인 매수세 유입 및 숏 스퀴즈 기대감, 분기배당 비교.</t>
+          <t>외국인 매수세 강세 및 숏 스퀴즈 기대감. HBM4 시장 경쟁 및 자사주 매입 관련 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['삼성전자우', '외국인매수', '숏스퀴즈']</t>
+          <t>['외국인 매수', '숏 스퀴즈', 'HBM4']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>239000</v>
+        <v>241000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+7.66%</t>
+          <t>'+8.56%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G7" t="n">
-        <v>2596</v>
+        <v>1962</v>
       </c>
       <c r="H7" t="n">
         <v>46.15</v>
@@ -1061,7 +1061,7 @@
         <v>231000</v>
       </c>
       <c r="L7" t="n">
-        <v>239500</v>
+        <v>241500</v>
       </c>
       <c r="M7" t="n">
         <v>228000</v>
@@ -1070,7 +1070,7 @@
         <v>46.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1254644572250</v>
+        <v>1442963650750</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>이스라엘 관련 뉴스 및 AI 대체 논의 속 기대감 형성, 삼성전자 이재용 언급.</t>
+          <t>미국 반도체 시장 경쟁 심화 속 HBM4 점유율 경쟁 전망. 외국인 매수세 유입 시 추가 상승 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['삼성전자', 'AI', '이스라엘']</t>
+          <t>['HBM4', '점유율', '외국인 매수']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1442000</v>
+        <v>1447000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+7.53%</t>
+          <t>'+7.90%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="G8" t="n">
-        <v>1418</v>
+        <v>1473</v>
       </c>
       <c r="H8" t="n">
         <v>48.61</v>
@@ -1153,7 +1153,7 @@
         <v>1390000</v>
       </c>
       <c r="L8" t="n">
-        <v>1442000</v>
+        <v>1452000</v>
       </c>
       <c r="M8" t="n">
         <v>1358000</v>
@@ -1162,7 +1162,7 @@
         <v>48.66</v>
       </c>
       <c r="O8" t="n">
-        <v>2128175795000</v>
+        <v>2381298827000</v>
       </c>
       <c r="P8" t="n">
         <v>2987000</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>컨퍼런스콜 호평 및 향후 100조 주주 환원 발표, 외인 순매수 재개 및 200 돌파 기대.</t>
+          <t>컨퍼런스 콜 호조 및 외국인 순매수세 강화. 내년 매출 증가 및 높은 수익성 기대감.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['SK하이닉스', '주주환원', '컨퍼런스콜']</t>
+          <t>['컨퍼런스 콜', '외국인 순매수', '수익성']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14460</v>
+        <v>17080</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+5.55%</t>
+          <t>'+7.90%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.05</v>
+        <v>1.02</v>
       </c>
       <c r="E9" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F9" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="G9" t="n">
-        <v>158</v>
+        <v>101</v>
       </c>
       <c r="H9" t="n">
-        <v>2.87</v>
+        <v>1.11</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>13700</v>
+        <v>15830</v>
       </c>
       <c r="K9" t="n">
-        <v>14210</v>
+        <v>17170</v>
       </c>
       <c r="L9" t="n">
-        <v>14800</v>
+        <v>17850</v>
       </c>
       <c r="M9" t="n">
-        <v>14210</v>
+        <v>15830</v>
       </c>
       <c r="N9" t="n">
-        <v>2.82</v>
+        <v>0.09</v>
       </c>
       <c r="O9" t="n">
-        <v>59489907180</v>
+        <v>118256527070</v>
       </c>
       <c r="P9" t="n">
-        <v>31500</v>
+        <v>28800</v>
       </c>
       <c r="Q9" t="n">
-        <v>1760</v>
+        <v>11550</v>
       </c>
       <c r="R9" t="n">
-        <v>203000</v>
+        <v>-78000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>광통신 섹터 내에서의 주가 상승 기대감과 외국인 프로그램 매수세 유입 정황. 3분기 실적 발표 및 공매도 세력의 움직임 주목.</t>
+          <t>멜콘, AI 데이터센터 방열 시스템 594억 공급 계약 및 마이크론 반도체 장비 평가 완료 뉴스. 삼성, 하이닉스 등 대형사 공급망 진입 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['광통신', '외국인 매수', '공매도']</t>
+          <t>['방열 시스템', '공급 계약', '반도체 장비']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NAVER</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>183000</v>
+        <v>14750</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.99%</t>
+          <t>'+7.66%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>382</v>
+        <v>67</v>
       </c>
       <c r="F10" t="n">
-        <v>234</v>
+        <v>34</v>
       </c>
       <c r="G10" t="n">
-        <v>1163</v>
+        <v>169</v>
       </c>
       <c r="H10" t="n">
-        <v>35.43</v>
+        <v>2.87</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>174300</v>
+        <v>13700</v>
       </c>
       <c r="K10" t="n">
-        <v>181100</v>
+        <v>14210</v>
       </c>
       <c r="L10" t="n">
-        <v>186900</v>
+        <v>14820</v>
       </c>
       <c r="M10" t="n">
-        <v>180000</v>
+        <v>14210</v>
       </c>
       <c r="N10" t="n">
-        <v>35.49</v>
+        <v>2.82</v>
       </c>
       <c r="O10" t="n">
-        <v>79501696750</v>
+        <v>69799054810</v>
       </c>
       <c r="P10" t="n">
-        <v>304000</v>
+        <v>31500</v>
       </c>
       <c r="Q10" t="n">
-        <v>170900</v>
+        <v>1760</v>
       </c>
       <c r="R10" t="n">
-        <v>-15000</v>
+        <v>203000</v>
       </c>
       <c r="S10" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>엔비디아의 최대 주주 부상 및 야간선물 상승. 대규모 호재 대비 주가 상승폭 미미 지적.</t>
+          <t>대한광통신, 광통신 3분기 실적 발표 및 외인 프로그램 매수세 유입. 루멘텀, 코히어런트 급등 영향.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['엔비디아', '최대 주주', '야간선물']</t>
+          <t>['광통신', '실적 발표', '외인 매수']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,77 +1384,77 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>035420</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>NAVER</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2250</v>
+        <v>182500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.69%</t>
+          <t>'+4.70%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.18</v>
+        <v>-0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>44</v>
+        <v>403</v>
       </c>
       <c r="F11" t="n">
-        <v>30</v>
+        <v>244</v>
       </c>
       <c r="G11" t="n">
-        <v>130</v>
+        <v>1205</v>
       </c>
       <c r="H11" t="n">
-        <v>5.07</v>
+        <v>35.43</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>2170</v>
+        <v>174300</v>
       </c>
       <c r="K11" t="n">
-        <v>2160</v>
+        <v>181100</v>
       </c>
       <c r="L11" t="n">
-        <v>2475</v>
+        <v>186900</v>
       </c>
       <c r="M11" t="n">
-        <v>2155</v>
+        <v>180000</v>
       </c>
       <c r="N11" t="n">
-        <v>4.89</v>
+        <v>35.49</v>
       </c>
       <c r="O11" t="n">
-        <v>36143231789</v>
+        <v>86213636400</v>
       </c>
       <c r="P11" t="n">
-        <v>4980</v>
+        <v>304000</v>
       </c>
       <c r="Q11" t="n">
-        <v>774</v>
+        <v>170900</v>
       </c>
       <c r="R11" t="n">
-        <v>410000</v>
+        <v>-15000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>로봇 섹터 강세 속 앤로보틱스의 주가 흐름에 대한 기대와 우려 혼재. 신용 물량 증가 및 단기 매매 세력의 움직임 관찰.</t>
+          <t>NAVER, 엔비디아 3대 주주 등극 및 야간 선물 폭등. 코어위브 상승 및 지수 대비 낮은 수익률 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['로봇 섹터', '신용 물량', '단기 매매']</t>
+          <t>['엔비디아', '야간 선물', '코어위브']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>035420</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8430</v>
+        <v>8510</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.80%</t>
+          <t>'+3.78%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.27</v>
       </c>
       <c r="E12" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="F12" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H12" t="n">
         <v>1.42</v>
@@ -1530,7 +1530,7 @@
         <v>1.15</v>
       </c>
       <c r="O12" t="n">
-        <v>34257612580</v>
+        <v>38766501670</v>
       </c>
       <c r="P12" t="n">
         <v>9820</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 양자, 보안주 급등과 국내 보안 사고 뉴스에 따른 IT 보안 섹터 관심 증대. 샌즈랩의 AI 시대 보안 역할 및 과거 보안 대장주 언급.</t>
+          <t>샌즈랩, 미국 양자 및 보안주 급등 영향. IT 보안 사고 뉴스 및 AI 데이터센터 방열 시스템 공급 계약 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['IT 보안', 'AI 시대', '해킹 사고']</t>
+          <t>['양자 보안', 'AI 보안', '데이터센터']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30300</v>
+        <v>63900</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.71%</t>
+          <t>'+2.73%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.01</v>
+        <v>0.57</v>
       </c>
       <c r="E13" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="F13" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G13" t="n">
-        <v>186</v>
+        <v>325</v>
       </c>
       <c r="H13" t="n">
-        <v>28.81</v>
+        <v>41.01</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>29500</v>
+        <v>62200</v>
       </c>
       <c r="K13" t="n">
-        <v>29900</v>
+        <v>63000</v>
       </c>
       <c r="L13" t="n">
-        <v>30650</v>
+        <v>64300</v>
       </c>
       <c r="M13" t="n">
-        <v>29900</v>
+        <v>62200</v>
       </c>
       <c r="N13" t="n">
-        <v>28.82</v>
+        <v>40.44</v>
       </c>
       <c r="O13" t="n">
-        <v>18657717925</v>
+        <v>117142423050</v>
       </c>
       <c r="P13" t="n">
-        <v>69700</v>
+        <v>67300</v>
       </c>
       <c r="Q13" t="n">
-        <v>29200</v>
+        <v>23150</v>
       </c>
       <c r="R13" t="n">
-        <v>132000</v>
+        <v>129000</v>
       </c>
       <c r="S13" t="n">
-        <v>30000</v>
+        <v>31000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>매도세 지속 및 3만원 이하 예상, 네이버와 비교 및 공매도 이슈.</t>
+          <t>중동 전쟁 종식 기대감 속 국제유가 하락. 최근 4일간 코스피 수익률 1위 달성 및 자사주 매입 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['카카오', '공매도', '네이버']</t>
+          <t>['중동 전쟁', '수익률', '자사주 매입']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>035720</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>63600</v>
+        <v>30300</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.25%</t>
+          <t>'+2.71%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.57</v>
+        <v>-0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="F14" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G14" t="n">
-        <v>301</v>
+        <v>228</v>
       </c>
       <c r="H14" t="n">
-        <v>41.01</v>
+        <v>28.81</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>62200</v>
+        <v>29500</v>
       </c>
       <c r="K14" t="n">
-        <v>63000</v>
+        <v>29900</v>
       </c>
       <c r="L14" t="n">
-        <v>64300</v>
+        <v>30650</v>
       </c>
       <c r="M14" t="n">
-        <v>62200</v>
+        <v>29900</v>
       </c>
       <c r="N14" t="n">
-        <v>40.44</v>
+        <v>28.82</v>
       </c>
       <c r="O14" t="n">
-        <v>111780919050</v>
+        <v>19363354500</v>
       </c>
       <c r="P14" t="n">
-        <v>67300</v>
+        <v>69700</v>
       </c>
       <c r="Q14" t="n">
-        <v>23150</v>
+        <v>29200</v>
       </c>
       <c r="R14" t="n">
-        <v>129000</v>
+        <v>132000</v>
       </c>
       <c r="S14" t="n">
-        <v>31000</v>
+        <v>30000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>이란 평화 회담 기대감 속 국제유가 하락, 코스피 수익률 1위 달성 및 자사주 매입 언급.</t>
+          <t>주가 부진 지속 및 공매도 관련 우려. 거래량 부족 시 추가 하락 가능성 제기.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['삼성E&amp;A', '국제유가', '자사주매입']</t>
+          <t>['주가 부진', '공매도', '거래량']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>035720</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16100</v>
+        <v>2220</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.71%</t>
+          <t>'+2.30%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.02</v>
+        <v>0.18</v>
       </c>
       <c r="E15" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F15" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G15" t="n">
-        <v>76</v>
+        <v>139</v>
       </c>
       <c r="H15" t="n">
-        <v>1.11</v>
+        <v>5.07</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>15830</v>
+        <v>2170</v>
       </c>
       <c r="K15" t="n">
-        <v>17170</v>
+        <v>2160</v>
       </c>
       <c r="L15" t="n">
-        <v>17300</v>
+        <v>2475</v>
       </c>
       <c r="M15" t="n">
-        <v>15830</v>
+        <v>2155</v>
       </c>
       <c r="N15" t="n">
-        <v>0.09</v>
+        <v>4.89</v>
       </c>
       <c r="O15" t="n">
-        <v>75269778170</v>
+        <v>37175130413</v>
       </c>
       <c r="P15" t="n">
-        <v>28800</v>
+        <v>4980</v>
       </c>
       <c r="Q15" t="n">
-        <v>11550</v>
+        <v>774</v>
       </c>
       <c r="R15" t="n">
-        <v>-78000</v>
+        <v>410000</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>AI 데이터센터 방열 시스템 공급 계약 및 삼성, 하이닉스와의 연관성을 바탕으로 한 밸류에이션 기대감. 보호예수 물량 해제와 수급 동향 주시.</t>
+          <t>로봇 섹터 강세 속 앤로보틱스, 삼성 로봇 테마 대장주 언급. 신용 증가 및 자사주 매도.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['AI 데이터센터', '방열 시스템', '밸류에이션']</t>
+          <t>['로봇 섹터', '삼성 로봇', '신용 증가']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16410</v>
+        <v>16300</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.12%</t>
+          <t>'-0.55%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="F16" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="G16" t="n">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="H16" t="n">
         <v>28.03</v>
@@ -1892,13 +1892,13 @@
         <v>16760</v>
       </c>
       <c r="M16" t="n">
-        <v>16350</v>
+        <v>16300</v>
       </c>
       <c r="N16" t="n">
         <v>27.96</v>
       </c>
       <c r="O16" t="n">
-        <v>17956045410</v>
+        <v>20729145635</v>
       </c>
       <c r="P16" t="n">
         <v>35350</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>외국인, 기관 프로그램 매수세 속 목표주가 하향 조정 및 신용 물량 주의보.</t>
+          <t>조선업종 전반의 부진 속 주가 하락. 목표주가 하향 조정 및 신용 물량 주의보.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['삼성중공업', '목표주가', '외국인매수']</t>
+          <t>['조선업', '주가 하락', '목표주가']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14370</v>
+        <v>14330</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-0.55%</t>
+          <t>'-0.83%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.19</v>
       </c>
       <c r="E17" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F17" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G17" t="n">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="H17" t="n">
         <v>9.83</v>
@@ -1990,7 +1990,7 @@
         <v>10.02</v>
       </c>
       <c r="O17" t="n">
-        <v>26081755140</v>
+        <v>28062682910</v>
       </c>
       <c r="P17" t="n">
         <v>40350</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>주가 하락 및 공매도에 대한 불만 표출. 목표가 하향 조정에 대한 부정적 의견.</t>
+          <t>주가 하락 및 경영진에 대한 불만 표출. 공매도 및 연기금 매도 관련 부정적 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['공매도', '주가 하락', '개잡주']</t>
+          <t>['주가 하락', '공매도', '연기금']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52100</v>
+        <v>51650</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-1.70%</t>
+          <t>'-2.55%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.03</v>
       </c>
       <c r="E18" t="n">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="F18" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="G18" t="n">
-        <v>660</v>
+        <v>698</v>
       </c>
       <c r="H18" t="n">
         <v>10.31</v>
@@ -2082,7 +2082,7 @@
         <v>10.34</v>
       </c>
       <c r="O18" t="n">
-        <v>39136525700</v>
+        <v>41826563500</v>
       </c>
       <c r="P18" t="n">
         <v>154800</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>강한 지수 반등에도 하락세 지속, 외인/프로그램 폭탄 매도 관찰.</t>
+          <t>주가 하락 및 증권가 리포트에 대한 불만. 공매도 및 외국인 폭탄 매도 관련 부정적 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['한화오션', '외인매도', '지수반등']</t>
+          <t>['주가 하락', '공매도', '외국인 매도']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1986</v>
+        <v>1978</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-4.75%</t>
+          <t>'-5.13%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.39</v>
       </c>
       <c r="E19" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F19" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G19" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H19" t="n">
         <v>2.52</v>
@@ -2174,7 +2174,7 @@
         <v>2.13</v>
       </c>
       <c r="O19" t="n">
-        <v>11230999466</v>
+        <v>11588335621</v>
       </c>
       <c r="P19" t="n">
         <v>6190</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>액면병합 이슈 속 개인 매도세 관찰, 긍정적 전망 언급 있으나 불확실.</t>
+          <t>액면병합 이후 주가 하락에 대한 의문 제기. 전망 관련 긍정적 언급 있으나, 불확실성 존재.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['액면병합', '개인매도', '전망']</t>
+          <t>['액면병합', '전망', '하락']</t>
         </is>
       </c>
       <c r="X19" t="n">

--- a/data/trending_integrated_20261028_10.xlsx
+++ b/data/trending_integrated_20261028_10.xlsx
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29050</v>
+        <v>3965</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+22.32%</t>
+          <t>'+22.76%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.15</v>
+        <v>-0.19</v>
       </c>
       <c r="E2" t="n">
+        <v>65</v>
+      </c>
+      <c r="F2" t="n">
         <v>45</v>
       </c>
-      <c r="F2" t="n">
-        <v>36</v>
-      </c>
       <c r="G2" t="n">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="H2" t="n">
-        <v>5.16</v>
+        <v>1.2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,38 +595,38 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>23750</v>
+        <v>3230</v>
       </c>
       <c r="K2" t="n">
-        <v>24200</v>
+        <v>3600</v>
       </c>
       <c r="L2" t="n">
-        <v>29900</v>
+        <v>3990</v>
       </c>
       <c r="M2" t="n">
-        <v>24200</v>
+        <v>3580</v>
       </c>
       <c r="N2" t="n">
-        <v>5.31</v>
+        <v>1.39</v>
       </c>
       <c r="O2" t="n">
-        <v>116207895725</v>
+        <v>93252720153</v>
       </c>
       <c r="P2" t="n">
-        <v>50600</v>
+        <v>8100</v>
       </c>
       <c r="Q2" t="n">
-        <v>13210</v>
+        <v>592</v>
       </c>
       <c r="R2" t="n">
-        <v>-15000</v>
+        <v>44000</v>
       </c>
       <c r="S2" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>원익홀딩스, 삼성 지분 투자 및 로봇 행사 관련 기대감. 이재용 회장 로봇 관련 행보 및 SK 입질 언급.</t>
+          <t>미국 광통신주 강세에 따른 기대감. 정부 수주 및 기술력 인정 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['로봇주', '삼성 투자', '이재용']</t>
+          <t>['광통신', '정부수주', '기술력']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3915</v>
+        <v>28950</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+21.21%</t>
+          <t>'+21.89%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.19</v>
+        <v>-0.15</v>
       </c>
       <c r="E3" t="n">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="F3" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G3" t="n">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2</v>
+        <v>5.16</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>3230</v>
+        <v>23750</v>
       </c>
       <c r="K3" t="n">
-        <v>3600</v>
+        <v>24200</v>
       </c>
       <c r="L3" t="n">
-        <v>3990</v>
+        <v>29900</v>
       </c>
       <c r="M3" t="n">
-        <v>3580</v>
+        <v>24200</v>
       </c>
       <c r="N3" t="n">
-        <v>1.39</v>
+        <v>5.31</v>
       </c>
       <c r="O3" t="n">
-        <v>83493241183</v>
+        <v>121982175125</v>
       </c>
       <c r="P3" t="n">
-        <v>8100</v>
+        <v>50600</v>
       </c>
       <c r="Q3" t="n">
-        <v>592</v>
+        <v>13210</v>
       </c>
       <c r="R3" t="n">
-        <v>44000</v>
+        <v>-15000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 광통신주 강세와 함께 상승 기대감. 갭 상승 후 매물대 돌파 시 추가 상승 전망.</t>
+          <t>원익홀딩스, 삼성 지분 투자 및 로봇 행사 관련 기대감. 이재용 회장 로봇 관련 행보 및 SK 입질 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['광통신', '갭 상승', '매물대']</t>
+          <t>['로봇주', '삼성 투자', '이재용']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,7 +740,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19030</v>
+        <v>19120</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+11.35%</t>
+          <t>'+11.88%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.61</v>
       </c>
       <c r="E4" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F4" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G4" t="n">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="H4" t="n">
         <v>4.74</v>
@@ -794,7 +794,7 @@
         <v>4.13</v>
       </c>
       <c r="O4" t="n">
-        <v>34215427790</v>
+        <v>35529140705</v>
       </c>
       <c r="P4" t="n">
         <v>28600</v>
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2675</v>
+        <v>17380</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+9.18%</t>
+          <t>'+9.79%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.68</v>
+        <v>1.02</v>
       </c>
       <c r="E5" t="n">
+        <v>82</v>
+      </c>
+      <c r="F5" t="n">
         <v>48</v>
       </c>
-      <c r="F5" t="n">
-        <v>34</v>
-      </c>
       <c r="G5" t="n">
-        <v>50</v>
+        <v>149</v>
       </c>
       <c r="H5" t="n">
-        <v>1.69</v>
+        <v>1.11</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2450</v>
+        <v>15830</v>
       </c>
       <c r="K5" t="n">
-        <v>2525</v>
+        <v>17170</v>
       </c>
       <c r="L5" t="n">
-        <v>2965</v>
+        <v>17920</v>
       </c>
       <c r="M5" t="n">
-        <v>2505</v>
+        <v>15830</v>
       </c>
       <c r="N5" t="n">
-        <v>1.01</v>
+        <v>0.09</v>
       </c>
       <c r="O5" t="n">
-        <v>56874860638</v>
+        <v>138882844055</v>
       </c>
       <c r="P5" t="n">
-        <v>2965</v>
+        <v>28800</v>
       </c>
       <c r="Q5" t="n">
-        <v>865</v>
+        <v>11550</v>
       </c>
       <c r="R5" t="n">
-        <v>1002000</v>
+        <v>-78000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈, 미국 1000억 규모 하이브리드 부품 수주 뉴스. 전환사채 전환 및 프로그램 매수세 유입.</t>
+          <t>멜콘, 미국 마이크론 반도체 장비 평가 완료 및 양산 공급 조율 소식. AI 데이터센터 방열 시스템 공급 계약 체결.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['하이브리드 부품', '전환사채', '프로그램 매수']</t>
+          <t>['마이크론', '반도체 장비', '공급 계약']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>419050</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>186500</v>
+        <v>187800</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.00%</t>
+          <t>'+9.76%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F6" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G6" t="n">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="H6" t="n">
         <v>74.90000000000001</v>
@@ -969,7 +969,7 @@
         <v>176300</v>
       </c>
       <c r="L6" t="n">
-        <v>187400</v>
+        <v>187900</v>
       </c>
       <c r="M6" t="n">
         <v>175400</v>
@@ -978,7 +978,7 @@
         <v>74.89</v>
       </c>
       <c r="O6" t="n">
-        <v>387819617500</v>
+        <v>418169017300</v>
       </c>
       <c r="P6" t="n">
         <v>243500</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>외국인 매수세 강세 및 숏 스퀴즈 기대감. HBM4 시장 경쟁 및 자사주 매입 관련 언급.</t>
+          <t>외국인 매수세와 숏 스퀴즈 가능성 언급. 자사주 매입 및 소각 기대감.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['외국인 매수', '숏 스퀴즈', 'HBM4']</t>
+          <t>['외국인', '숏 스퀴즈', '자사주']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,83 +1023,83 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>241000</v>
+        <v>2680</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.56%</t>
+          <t>'+9.39%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.05</v>
+        <v>0.68</v>
       </c>
       <c r="E7" t="n">
-        <v>800</v>
+        <v>50</v>
       </c>
       <c r="F7" t="n">
-        <v>421</v>
+        <v>35</v>
       </c>
       <c r="G7" t="n">
-        <v>1962</v>
+        <v>52</v>
       </c>
       <c r="H7" t="n">
-        <v>46.15</v>
+        <v>1.69</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>222000</v>
+        <v>2450</v>
       </c>
       <c r="K7" t="n">
-        <v>231000</v>
+        <v>2525</v>
       </c>
       <c r="L7" t="n">
-        <v>241500</v>
+        <v>2965</v>
       </c>
       <c r="M7" t="n">
-        <v>228000</v>
+        <v>2505</v>
       </c>
       <c r="N7" t="n">
-        <v>46.1</v>
+        <v>1.01</v>
       </c>
       <c r="O7" t="n">
-        <v>1442963650750</v>
+        <v>58504646874</v>
       </c>
       <c r="P7" t="n">
-        <v>374500</v>
+        <v>2965</v>
       </c>
       <c r="Q7" t="n">
-        <v>94500</v>
+        <v>865</v>
       </c>
       <c r="R7" t="n">
-        <v>539000</v>
+        <v>1002000</v>
       </c>
       <c r="S7" t="n">
-        <v>339000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 반도체 시장 경쟁 심화 속 HBM4 점유율 경쟁 전망. 외국인 매수세 유입 시 추가 상승 기대.</t>
+          <t>미국 현지 1000억원 규모 하이브리드 부품 수주 소식. 개인 물량 흡수 및 3000원 돌파 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['HBM4', '점유율', '외국인 매수']</t>
+          <t>['수주', '하이브리드 부품', '전환사채']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>419050</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1447000</v>
+        <v>242000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+7.90%</t>
+          <t>'+9.01%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="E8" t="n">
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>470</v>
+        <v>438</v>
       </c>
       <c r="G8" t="n">
-        <v>1473</v>
+        <v>1715</v>
       </c>
       <c r="H8" t="n">
-        <v>48.61</v>
+        <v>46.15</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,47 +1147,47 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1341000</v>
+        <v>222000</v>
       </c>
       <c r="K8" t="n">
-        <v>1390000</v>
+        <v>231000</v>
       </c>
       <c r="L8" t="n">
-        <v>1452000</v>
+        <v>242500</v>
       </c>
       <c r="M8" t="n">
-        <v>1358000</v>
+        <v>228000</v>
       </c>
       <c r="N8" t="n">
-        <v>48.66</v>
+        <v>46.1</v>
       </c>
       <c r="O8" t="n">
-        <v>2381298827000</v>
+        <v>1545989868750</v>
       </c>
       <c r="P8" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q8" t="n">
-        <v>501000</v>
+        <v>94500</v>
       </c>
       <c r="R8" t="n">
-        <v>-77000</v>
+        <v>539000</v>
       </c>
       <c r="S8" t="n">
-        <v>25000</v>
+        <v>339000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>컨퍼런스 콜 호조 및 외국인 순매수세 강화. 내년 매출 증가 및 높은 수익성 기대감.</t>
+          <t>높은 주주환원 기대감과 HBM4 점유율 경쟁력 언급. 26만전자 및 80만원 목표가 제시.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['컨퍼런스 콜', '외국인 순매수', '수익성']</t>
+          <t>['주주환원', 'HBM4', '실적']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,77 +1200,77 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17080</v>
+        <v>1459000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+7.90%</t>
+          <t>'+8.80%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.02</v>
+        <v>-0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>70</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>44</v>
+        <v>468</v>
       </c>
       <c r="G9" t="n">
-        <v>101</v>
+        <v>1595</v>
       </c>
       <c r="H9" t="n">
-        <v>1.11</v>
+        <v>48.61</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>15830</v>
+        <v>1341000</v>
       </c>
       <c r="K9" t="n">
-        <v>17170</v>
+        <v>1390000</v>
       </c>
       <c r="L9" t="n">
-        <v>17850</v>
+        <v>1460000</v>
       </c>
       <c r="M9" t="n">
-        <v>15830</v>
+        <v>1358000</v>
       </c>
       <c r="N9" t="n">
-        <v>0.09</v>
+        <v>48.66</v>
       </c>
       <c r="O9" t="n">
-        <v>118256527070</v>
+        <v>2518052221500</v>
       </c>
       <c r="P9" t="n">
-        <v>28800</v>
+        <v>2987000</v>
       </c>
       <c r="Q9" t="n">
-        <v>11550</v>
+        <v>501000</v>
       </c>
       <c r="R9" t="n">
-        <v>-78000</v>
+        <v>-77000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>멜콘, AI 데이터센터 방열 시스템 594억 공급 계약 및 마이크론 반도체 장비 평가 완료 뉴스. 삼성, 하이닉스 등 대형사 공급망 진입 기대.</t>
+          <t>컨퍼런스콜 성공적 마무리 및 외인 순매수 재개. HBM 시장 경쟁력과 주주환원 정책 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['방열 시스템', '공급 계약', '반도체 장비']</t>
+          <t>['컨콜', 'HBM', '주주환원']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14750</v>
+        <v>14670</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+7.66%</t>
+          <t>'+7.08%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F10" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G10" t="n">
-        <v>169</v>
+        <v>218</v>
       </c>
       <c r="H10" t="n">
         <v>2.87</v>
@@ -1346,7 +1346,7 @@
         <v>2.82</v>
       </c>
       <c r="O10" t="n">
-        <v>69799054810</v>
+        <v>74569891435</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>대한광통신, 광통신 3분기 실적 발표 및 외인 프로그램 매수세 유입. 루멘텀, 코히어런트 급등 영향.</t>
+          <t>대한광통신, 메타 유리기판 및 해상광통신 케이블 관련 기대감 속 외인 매수세 유입. 3분기 실적 발표 예정.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['광통신', '실적 발표', '외인 매수']</t>
+          <t>['유리기판', '해상광통신', '외인 매수']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>182500</v>
+        <v>182900</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+4.70%</t>
+          <t>'+4.93%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="F11" t="n">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="G11" t="n">
-        <v>1205</v>
+        <v>1262</v>
       </c>
       <c r="H11" t="n">
         <v>35.43</v>
@@ -1438,7 +1438,7 @@
         <v>35.49</v>
       </c>
       <c r="O11" t="n">
-        <v>86213636400</v>
+        <v>88519550400</v>
       </c>
       <c r="P11" t="n">
         <v>304000</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8510</v>
+        <v>8550</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+3.78%</t>
+          <t>'+4.27%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.27</v>
       </c>
       <c r="E12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G12" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H12" t="n">
         <v>1.42</v>
@@ -1530,7 +1530,7 @@
         <v>1.15</v>
       </c>
       <c r="O12" t="n">
-        <v>38766501670</v>
+        <v>40985577900</v>
       </c>
       <c r="P12" t="n">
         <v>9820</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>샌즈랩, 미국 양자 및 보안주 급등 영향. IT 보안 사고 뉴스 및 AI 데이터센터 방열 시스템 공급 계약 언급.</t>
+          <t>미국 양자·보안주 급등 및 연이은 해킹 사고 발생으로 샌즈랩 등 보안주에 대한 관심 증대. AI 시대 보안 중요성 부각.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['양자 보안', 'AI 보안', '데이터센터']</t>
+          <t>['보안주', '해킹 사고', 'AI 시대']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,79 +1575,79 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>63900</v>
+        <v>2240</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.73%</t>
+          <t>'+3.23%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.57</v>
+        <v>0.18</v>
       </c>
       <c r="E13" t="n">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="F13" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="G13" t="n">
-        <v>325</v>
+        <v>145</v>
       </c>
       <c r="H13" t="n">
-        <v>41.01</v>
+        <v>5.07</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>62200</v>
+        <v>2170</v>
       </c>
       <c r="K13" t="n">
-        <v>63000</v>
+        <v>2160</v>
       </c>
       <c r="L13" t="n">
-        <v>64300</v>
+        <v>2475</v>
       </c>
       <c r="M13" t="n">
-        <v>62200</v>
+        <v>2155</v>
       </c>
       <c r="N13" t="n">
-        <v>40.44</v>
+        <v>4.89</v>
       </c>
       <c r="O13" t="n">
-        <v>117142423050</v>
+        <v>37602479322</v>
       </c>
       <c r="P13" t="n">
-        <v>67300</v>
+        <v>4980</v>
       </c>
       <c r="Q13" t="n">
-        <v>23150</v>
+        <v>774</v>
       </c>
       <c r="R13" t="n">
-        <v>129000</v>
+        <v>410000</v>
       </c>
       <c r="S13" t="n">
-        <v>31000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>중동 전쟁 종식 기대감 속 국제유가 하락. 최근 4일간 코스피 수익률 1위 달성 및 자사주 매입 기대.</t>
+          <t>로봇 섹터 강세 속 앤로보틱스 주가 움직임에 대한 기대와 우려가 공존. 자사주 매도 및 신용 증가 등 혼조세.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['중동 전쟁', '수익률', '자사주 매입']</t>
+          <t>['로봇 섹터', '신용 증가', '자사주 매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30300</v>
+        <v>64150</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.71%</t>
+          <t>'+3.14%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.01</v>
+        <v>0.57</v>
       </c>
       <c r="E14" t="n">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="F14" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G14" t="n">
-        <v>228</v>
+        <v>342</v>
       </c>
       <c r="H14" t="n">
-        <v>28.81</v>
+        <v>41.01</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>29500</v>
+        <v>62200</v>
       </c>
       <c r="K14" t="n">
-        <v>29900</v>
+        <v>63000</v>
       </c>
       <c r="L14" t="n">
-        <v>30650</v>
+        <v>64300</v>
       </c>
       <c r="M14" t="n">
-        <v>29900</v>
+        <v>62200</v>
       </c>
       <c r="N14" t="n">
-        <v>28.82</v>
+        <v>40.44</v>
       </c>
       <c r="O14" t="n">
-        <v>19363354500</v>
+        <v>120940126950</v>
       </c>
       <c r="P14" t="n">
-        <v>69700</v>
+        <v>67300</v>
       </c>
       <c r="Q14" t="n">
-        <v>29200</v>
+        <v>23150</v>
       </c>
       <c r="R14" t="n">
-        <v>132000</v>
+        <v>129000</v>
       </c>
       <c r="S14" t="n">
-        <v>30000</v>
+        <v>31000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>주가 부진 지속 및 공매도 관련 우려. 거래량 부족 시 추가 하락 가능성 제기.</t>
+          <t>최근 코스피 수익률 1위 달성 및 중동 전쟁 종전 기대감. 공매도 감소 및 자사주 매입 효과 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['주가 부진', '공매도', '거래량']</t>
+          <t>['수익률', '전쟁종전', '자사주']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>035720</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2220</v>
+        <v>30250</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.30%</t>
+          <t>'+2.54%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.18</v>
+        <v>-0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F15" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="G15" t="n">
-        <v>139</v>
+        <v>254</v>
       </c>
       <c r="H15" t="n">
-        <v>5.07</v>
+        <v>28.81</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>2170</v>
+        <v>29500</v>
       </c>
       <c r="K15" t="n">
-        <v>2160</v>
+        <v>29900</v>
       </c>
       <c r="L15" t="n">
-        <v>2475</v>
+        <v>30650</v>
       </c>
       <c r="M15" t="n">
-        <v>2155</v>
+        <v>29900</v>
       </c>
       <c r="N15" t="n">
-        <v>4.89</v>
+        <v>28.82</v>
       </c>
       <c r="O15" t="n">
-        <v>37175130413</v>
+        <v>19671242725</v>
       </c>
       <c r="P15" t="n">
-        <v>4980</v>
+        <v>69700</v>
       </c>
       <c r="Q15" t="n">
-        <v>774</v>
+        <v>29200</v>
       </c>
       <c r="R15" t="n">
-        <v>410000</v>
+        <v>132000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>로봇 섹터 강세 속 앤로보틱스, 삼성 로봇 테마 대장주 언급. 신용 증가 및 자사주 매도.</t>
+          <t>주가 하락세 지속 및 네이버와의 비교. 거래량 부진 시 추가 하락 가능성 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['로봇 섹터', '삼성 로봇', '신용 증가']</t>
+          <t>['주가', '하락', '거래량']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>035720</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16300</v>
+        <v>16360</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-0.55%</t>
+          <t>'-0.18%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F16" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G16" t="n">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="H16" t="n">
         <v>28.03</v>
@@ -1898,7 +1898,7 @@
         <v>27.96</v>
       </c>
       <c r="O16" t="n">
-        <v>20729145635</v>
+        <v>22323036110</v>
       </c>
       <c r="P16" t="n">
         <v>35350</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>조선업종 전반의 부진 속 주가 하락. 목표주가 하향 조정 및 신용 물량 주의보.</t>
+          <t>주문량 대비 주가 부진에 대한 불만 제기. 목표주가 하향 조정 및 신용물량 주의보 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['조선업', '주가 하락', '목표주가']</t>
+          <t>['수주', '목표주가', '신용물량']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14330</v>
+        <v>14350</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-0.83%</t>
+          <t>'-0.69%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.19</v>
       </c>
       <c r="E17" t="n">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="F17" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G17" t="n">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="H17" t="n">
         <v>9.83</v>
@@ -1990,7 +1990,7 @@
         <v>10.02</v>
       </c>
       <c r="O17" t="n">
-        <v>28062682910</v>
+        <v>28759519845</v>
       </c>
       <c r="P17" t="n">
         <v>40350</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>51650</v>
+        <v>51900</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.55%</t>
+          <t>'-2.08%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.03</v>
       </c>
       <c r="E18" t="n">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="F18" t="n">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="G18" t="n">
-        <v>698</v>
+        <v>739</v>
       </c>
       <c r="H18" t="n">
         <v>10.31</v>
@@ -2082,7 +2082,7 @@
         <v>10.34</v>
       </c>
       <c r="O18" t="n">
-        <v>41826563500</v>
+        <v>43682132200</v>
       </c>
       <c r="P18" t="n">
         <v>154800</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>주가 하락 및 증권가 리포트에 대한 불만. 공매도 및 외국인 폭탄 매도 관련 부정적 언급.</t>
+          <t>코스피 강세에도 불구하고 주가 하락에 대한 불만 토로. 외인 매도세 및 악재 지속.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['주가 하락', '공매도', '외국인 매도']</t>
+          <t>['공매도', '악재', '매도세']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1978</v>
+        <v>1986</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-5.13%</t>
+          <t>'-4.75%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.39</v>
       </c>
       <c r="E19" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F19" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G19" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H19" t="n">
         <v>2.52</v>
@@ -2174,7 +2174,7 @@
         <v>2.13</v>
       </c>
       <c r="O19" t="n">
-        <v>11588335621</v>
+        <v>11714635143</v>
       </c>
       <c r="P19" t="n">
         <v>6190</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>액면병합 이후 주가 하락에 대한 의문 제기. 전망 관련 긍정적 언급 있으나, 불확실성 존재.</t>
+          <t>액면병합 가격 대비 주가 하락에 대한 의문 제기. 공매도 및 대차 물량 증가 추정.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['액면병합', '전망', '하락']</t>
+          <t>['액면병합', '공매도', '대차']</t>
         </is>
       </c>
       <c r="X19" t="n">

--- a/data/trending_integrated_20261028_10.xlsx
+++ b/data/trending_integrated_20261028_10.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3965</v>
+        <v>4075</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+22.76%</t>
+          <t>'+26.16%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.19</v>
       </c>
       <c r="E2" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F2" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G2" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="H2" t="n">
         <v>1.2</v>
@@ -601,7 +601,7 @@
         <v>3600</v>
       </c>
       <c r="L2" t="n">
-        <v>3990</v>
+        <v>4120</v>
       </c>
       <c r="M2" t="n">
         <v>3580</v>
@@ -610,7 +610,7 @@
         <v>1.39</v>
       </c>
       <c r="O2" t="n">
-        <v>93252720153</v>
+        <v>108536376265</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미국 광통신주 강세에 따른 기대감. 정부 수주 및 기술력 인정 언급.</t>
+          <t>빛과전자, 미국 통신주 강세 및 공모 계약 체결로 인한 급등 기대감.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['광통신', '정부수주', '기술력']</t>
+          <t>['광통신', '공모계약', 'RFHIC']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28950</v>
+        <v>29000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+21.89%</t>
+          <t>'+22.11%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.15</v>
       </c>
       <c r="E3" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G3" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="H3" t="n">
         <v>5.16</v>
@@ -702,7 +702,7 @@
         <v>5.31</v>
       </c>
       <c r="O3" t="n">
-        <v>121982175125</v>
+        <v>127977202100</v>
       </c>
       <c r="P3" t="n">
         <v>50600</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>원익홀딩스, 삼성 지분 투자 및 로봇 행사 관련 기대감. 이재용 회장 로봇 관련 행보 및 SK 입질 언급.</t>
+          <t>원익홀딩스, 로봇 관련주로 주목받으며 기대감 형성. 다만, 구체적인 호재보다는 기대감에 따른 변동성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['로봇주', '삼성 투자', '이재용']</t>
+          <t>['로봇', '품절주', '인수']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>나무가</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19120</v>
+        <v>18060</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+11.88%</t>
+          <t>'+14.09%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.61</v>
+        <v>1.02</v>
       </c>
       <c r="E4" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="F4" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G4" t="n">
-        <v>255</v>
+        <v>207</v>
       </c>
       <c r="H4" t="n">
-        <v>4.74</v>
+        <v>1.11</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>17090</v>
+        <v>15830</v>
       </c>
       <c r="K4" t="n">
-        <v>19270</v>
+        <v>17170</v>
       </c>
       <c r="L4" t="n">
-        <v>20450</v>
+        <v>18530</v>
       </c>
       <c r="M4" t="n">
-        <v>18070</v>
+        <v>15830</v>
       </c>
       <c r="N4" t="n">
-        <v>4.13</v>
+        <v>0.09</v>
       </c>
       <c r="O4" t="n">
-        <v>35529140705</v>
+        <v>167530281220</v>
       </c>
       <c r="P4" t="n">
-        <v>28600</v>
+        <v>28800</v>
       </c>
       <c r="Q4" t="n">
-        <v>11050</v>
+        <v>11550</v>
       </c>
       <c r="R4" t="n">
-        <v>-83000</v>
+        <v>-78000</v>
       </c>
       <c r="S4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>나무가, 휴머노이드 로봇 '아틀라스' 1만대 발주 및 삼성 공급망 포함. 로봇 눈 신사업 및 VR 모듈 언급.</t>
+          <t>멜콘, 美 마이크론 반도체 장비 평가 완료 및 양산 공급 계약 체결. 삼성전자, SK하이닉스에 이어 마이크론까지 3대 반도체 기업 공급망 진입 확인.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['휴머노이드 로봇', '아틀라스', '삼성 공급망']</t>
+          <t>['반도체 장비', '공급망', 'AI 데이터센터']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>190510</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>나무가</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17380</v>
+        <v>18960</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+9.79%</t>
+          <t>'+10.94%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.02</v>
+        <v>0.61</v>
       </c>
       <c r="E5" t="n">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="F5" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G5" t="n">
-        <v>149</v>
+        <v>269</v>
       </c>
       <c r="H5" t="n">
-        <v>1.11</v>
+        <v>4.74</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>15830</v>
+        <v>17090</v>
       </c>
       <c r="K5" t="n">
-        <v>17170</v>
+        <v>19270</v>
       </c>
       <c r="L5" t="n">
-        <v>17920</v>
+        <v>20450</v>
       </c>
       <c r="M5" t="n">
-        <v>15830</v>
+        <v>18070</v>
       </c>
       <c r="N5" t="n">
-        <v>0.09</v>
+        <v>4.13</v>
       </c>
       <c r="O5" t="n">
-        <v>138882844055</v>
+        <v>36656764865</v>
       </c>
       <c r="P5" t="n">
-        <v>28800</v>
+        <v>28600</v>
       </c>
       <c r="Q5" t="n">
-        <v>11550</v>
+        <v>11050</v>
       </c>
       <c r="R5" t="n">
-        <v>-78000</v>
+        <v>-83000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>멜콘, 미국 마이크론 반도체 장비 평가 완료 및 양산 공급 조율 소식. AI 데이터센터 방열 시스템 공급 계약 체결.</t>
+          <t>나무가, 미국 휴머노이드 로봇 '아틀라스' 1만대 발주 관련 수혜 기대. 삼성, 현대차 등 주요 기업들과의 연관성 부각.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['마이크론', '반도체 장비', '공급 계약']</t>
+          <t>['휴머노이드', '로봇 부품', '아틀라스']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>190510</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
         <v>48</v>
       </c>
       <c r="G6" t="n">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="H6" t="n">
         <v>74.90000000000001</v>
@@ -969,7 +969,7 @@
         <v>176300</v>
       </c>
       <c r="L6" t="n">
-        <v>187900</v>
+        <v>189000</v>
       </c>
       <c r="M6" t="n">
         <v>175400</v>
@@ -978,7 +978,7 @@
         <v>74.89</v>
       </c>
       <c r="O6" t="n">
-        <v>418169017300</v>
+        <v>454069557050</v>
       </c>
       <c r="P6" t="n">
         <v>243500</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>외국인 매수세와 숏 스퀴즈 가능성 언급. 자사주 매입 및 소각 기대감.</t>
+          <t>삼성전자우, 외국인 매수세 및 숏 스퀴즈 가능성 언급. 자사주 매입 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['외국인', '숏 스퀴즈', '자사주']</t>
+          <t>['숏 스퀴즈', '자사주매입', '우선주']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2680</v>
+        <v>2685</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.39%</t>
+          <t>'+9.59%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.68</v>
       </c>
       <c r="E7" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F7" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G7" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="H7" t="n">
         <v>1.69</v>
@@ -1070,7 +1070,7 @@
         <v>1.01</v>
       </c>
       <c r="O7" t="n">
-        <v>58504646874</v>
+        <v>59829424845</v>
       </c>
       <c r="P7" t="n">
         <v>2965</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 현지 1000억원 규모 하이브리드 부품 수주 소식. 개인 물량 흡수 및 3000원 돌파 기대.</t>
+          <t>삼기에너지솔루션즈, 미국 1000억원 규모 하이브리드 부품 수주 및 개인 물량 흡수 후 상승 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['수주', '하이브리드 부품', '전환사채']</t>
+          <t>['수주', '하이브리드', '부품']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>242000</v>
+        <v>1459000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+9.01%</t>
+          <t>'+8.80%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E8" t="n">
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>438</v>
+        <v>468</v>
       </c>
       <c r="G8" t="n">
-        <v>1715</v>
+        <v>1744</v>
       </c>
       <c r="H8" t="n">
-        <v>46.15</v>
+        <v>48.61</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,47 +1147,47 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>222000</v>
+        <v>1341000</v>
       </c>
       <c r="K8" t="n">
-        <v>231000</v>
+        <v>1390000</v>
       </c>
       <c r="L8" t="n">
-        <v>242500</v>
+        <v>1465000</v>
       </c>
       <c r="M8" t="n">
-        <v>228000</v>
+        <v>1358000</v>
       </c>
       <c r="N8" t="n">
-        <v>46.1</v>
+        <v>48.66</v>
       </c>
       <c r="O8" t="n">
-        <v>1545989868750</v>
+        <v>2698178464000</v>
       </c>
       <c r="P8" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q8" t="n">
-        <v>94500</v>
+        <v>501000</v>
       </c>
       <c r="R8" t="n">
-        <v>539000</v>
+        <v>-77000</v>
       </c>
       <c r="S8" t="n">
-        <v>339000</v>
+        <v>25000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>높은 주주환원 기대감과 HBM4 점유율 경쟁력 언급. 26만전자 및 80만원 목표가 제시.</t>
+          <t>SK하이닉스, HBM 완판 및 컨퍼런스콜 호평으로 인한 강한 상승 기대감.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['주주환원', 'HBM4', '실적']</t>
+          <t>['HBM', '컨퍼런스콜', '완판']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1459000</v>
+        <v>240750</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+8.80%</t>
+          <t>'+8.45%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="E9" t="n">
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="G9" t="n">
-        <v>1595</v>
+        <v>1781</v>
       </c>
       <c r="H9" t="n">
-        <v>48.61</v>
+        <v>46.15</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,47 +1239,47 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1341000</v>
+        <v>222000</v>
       </c>
       <c r="K9" t="n">
-        <v>1390000</v>
+        <v>231000</v>
       </c>
       <c r="L9" t="n">
-        <v>1460000</v>
+        <v>243000</v>
       </c>
       <c r="M9" t="n">
-        <v>1358000</v>
+        <v>228000</v>
       </c>
       <c r="N9" t="n">
-        <v>48.66</v>
+        <v>46.1</v>
       </c>
       <c r="O9" t="n">
-        <v>2518052221500</v>
+        <v>1700297146000</v>
       </c>
       <c r="P9" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q9" t="n">
-        <v>501000</v>
+        <v>94500</v>
       </c>
       <c r="R9" t="n">
-        <v>-77000</v>
+        <v>539000</v>
       </c>
       <c r="S9" t="n">
-        <v>25000</v>
+        <v>339000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>컨퍼런스콜 성공적 마무리 및 외인 순매수 재개. HBM 시장 경쟁력과 주주환원 정책 언급.</t>
+          <t>삼성전자, HBM4 점유율 경쟁 및 26만전자 전망. 공매도 관련 논쟁.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['컨콜', 'HBM', '주주환원']</t>
+          <t>['HBM4', '영업이익', '공매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14670</v>
+        <v>14770</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+7.08%</t>
+          <t>'+7.81%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G10" t="n">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="H10" t="n">
         <v>2.87</v>
@@ -1337,7 +1337,7 @@
         <v>14210</v>
       </c>
       <c r="L10" t="n">
-        <v>14820</v>
+        <v>14870</v>
       </c>
       <c r="M10" t="n">
         <v>14210</v>
@@ -1346,7 +1346,7 @@
         <v>2.82</v>
       </c>
       <c r="O10" t="n">
-        <v>74569891435</v>
+        <v>83489860310</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>대한광통신, 메타 유리기판 및 해상광통신 케이블 관련 기대감 속 외인 매수세 유입. 3분기 실적 발표 예정.</t>
+          <t>대한광통신, 메타버스 관련 유리기판 해상광통신 케이블 수혜 기대감. 외국인 프로그램 매수세 유입.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['유리기판', '해상광통신', '외인 매수']</t>
+          <t>['해상광통신', '유리기판', '메타버스']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>182900</v>
+        <v>183900</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+4.93%</t>
+          <t>'+5.51%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>421</v>
+        <v>443</v>
       </c>
       <c r="F11" t="n">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="G11" t="n">
-        <v>1262</v>
+        <v>1304</v>
       </c>
       <c r="H11" t="n">
         <v>35.43</v>
@@ -1438,7 +1438,7 @@
         <v>35.49</v>
       </c>
       <c r="O11" t="n">
-        <v>88519550400</v>
+        <v>93230966650</v>
       </c>
       <c r="P11" t="n">
         <v>304000</v>
@@ -1487,21 +1487,21 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8550</v>
+        <v>8620</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+4.27%</t>
+          <t>'+5.12%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.27</v>
       </c>
       <c r="E12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G12" t="n">
         <v>65</v>
@@ -1530,7 +1530,7 @@
         <v>1.15</v>
       </c>
       <c r="O12" t="n">
-        <v>40985577900</v>
+        <v>43013763980</v>
       </c>
       <c r="P12" t="n">
         <v>9820</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 양자·보안주 급등 및 연이은 해킹 사고 발생으로 샌즈랩 등 보안주에 대한 관심 증대. AI 시대 보안 중요성 부각.</t>
+          <t>샌즈랩, 미국 양자컴퓨터 및 보안주 강세와 국내 IT 보안 사고 뉴스에 따른 관심 증가. AI 시대 보안 중요성 부각.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['보안주', '해킹 사고', 'AI 시대']</t>
+          <t>['AI 보안', '양자컴퓨터', 'IT 보안']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,79 +1575,79 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2240</v>
+        <v>64500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.23%</t>
+          <t>'+3.70%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.18</v>
+        <v>0.57</v>
       </c>
       <c r="E13" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="F13" t="n">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="G13" t="n">
-        <v>145</v>
+        <v>353</v>
       </c>
       <c r="H13" t="n">
-        <v>5.07</v>
+        <v>41.01</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>2170</v>
+        <v>62200</v>
       </c>
       <c r="K13" t="n">
-        <v>2160</v>
+        <v>63000</v>
       </c>
       <c r="L13" t="n">
-        <v>2475</v>
+        <v>64500</v>
       </c>
       <c r="M13" t="n">
-        <v>2155</v>
+        <v>62200</v>
       </c>
       <c r="N13" t="n">
-        <v>4.89</v>
+        <v>40.44</v>
       </c>
       <c r="O13" t="n">
-        <v>37602479322</v>
+        <v>130416713800</v>
       </c>
       <c r="P13" t="n">
-        <v>4980</v>
+        <v>67300</v>
       </c>
       <c r="Q13" t="n">
-        <v>774</v>
+        <v>23150</v>
       </c>
       <c r="R13" t="n">
-        <v>410000</v>
+        <v>129000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>31000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>로봇 섹터 강세 속 앤로보틱스 주가 움직임에 대한 기대와 우려가 공존. 자사주 매도 및 신용 증가 등 혼조세.</t>
+          <t>삼성E&amp;A, 최근 코스피 수익률 1위 달성 및 중동 전쟁 종전 기대감으로 인한 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['로봇 섹터', '신용 증가', '자사주 매도']</t>
+          <t>['수익률', '종전', '자사주매입']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>64150</v>
+        <v>30450</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+3.14%</t>
+          <t>'+3.22%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.57</v>
+        <v>-0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F14" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="G14" t="n">
-        <v>342</v>
+        <v>255</v>
       </c>
       <c r="H14" t="n">
-        <v>41.01</v>
+        <v>28.81</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>62200</v>
+        <v>29500</v>
       </c>
       <c r="K14" t="n">
-        <v>63000</v>
+        <v>29900</v>
       </c>
       <c r="L14" t="n">
-        <v>64300</v>
+        <v>30650</v>
       </c>
       <c r="M14" t="n">
-        <v>62200</v>
+        <v>29900</v>
       </c>
       <c r="N14" t="n">
-        <v>40.44</v>
+        <v>28.82</v>
       </c>
       <c r="O14" t="n">
-        <v>120940126950</v>
+        <v>20701593950</v>
       </c>
       <c r="P14" t="n">
-        <v>67300</v>
+        <v>69700</v>
       </c>
       <c r="Q14" t="n">
-        <v>23150</v>
+        <v>29200</v>
       </c>
       <c r="R14" t="n">
-        <v>129000</v>
+        <v>132000</v>
       </c>
       <c r="S14" t="n">
-        <v>31000</v>
+        <v>30000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>최근 코스피 수익률 1위 달성 및 중동 전쟁 종전 기대감. 공매도 감소 및 자사주 매입 효과 언급.</t>
+          <t>카카오, 주가 하락세 지속 및 낮은 적정 가치에 대한 부정적 의견. 거래량 부진 시 추가 하락 가능성 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['수익률', '전쟁종전', '자사주']</t>
+          <t>['적정주가', '하락세', '거래량']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>035720</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30250</v>
+        <v>2235</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.54%</t>
+          <t>'+3.00%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.01</v>
+        <v>0.18</v>
       </c>
       <c r="E15" t="n">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="F15" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="G15" t="n">
-        <v>254</v>
+        <v>154</v>
       </c>
       <c r="H15" t="n">
-        <v>28.81</v>
+        <v>5.07</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>29500</v>
+        <v>2170</v>
       </c>
       <c r="K15" t="n">
-        <v>29900</v>
+        <v>2160</v>
       </c>
       <c r="L15" t="n">
-        <v>30650</v>
+        <v>2475</v>
       </c>
       <c r="M15" t="n">
-        <v>29900</v>
+        <v>2155</v>
       </c>
       <c r="N15" t="n">
-        <v>28.82</v>
+        <v>4.89</v>
       </c>
       <c r="O15" t="n">
-        <v>19671242725</v>
+        <v>38659815191</v>
       </c>
       <c r="P15" t="n">
-        <v>69700</v>
+        <v>4980</v>
       </c>
       <c r="Q15" t="n">
-        <v>29200</v>
+        <v>774</v>
       </c>
       <c r="R15" t="n">
-        <v>132000</v>
+        <v>410000</v>
       </c>
       <c r="S15" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>주가 하락세 지속 및 네이버와의 비교. 거래량 부진 시 추가 하락 가능성 언급.</t>
+          <t>로봇 섹터 강세 속 앤로보틱스 주가 움직임에 대한 기대와 우려가 공존. 자사주 매도 및 신용 증가 등 혼조세.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['주가', '하락', '거래량']</t>
+          <t>['로봇 섹터', '신용 증가', '자사주 매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>035720</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16360</v>
+        <v>16460</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-0.18%</t>
+          <t>'+0.43%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F16" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G16" t="n">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="H16" t="n">
         <v>28.03</v>
@@ -1898,7 +1898,7 @@
         <v>27.96</v>
       </c>
       <c r="O16" t="n">
-        <v>22323036110</v>
+        <v>25588184595</v>
       </c>
       <c r="P16" t="n">
         <v>35350</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>주문량 대비 주가 부진에 대한 불만 제기. 목표주가 하향 조정 및 신용물량 주의보 언급.</t>
+          <t>삼성중공업, 조선업 불황 속 목표주가 하향 조정 및 공매도 우려.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['수주', '목표주가', '신용물량']</t>
+          <t>['공매도', '목표주가', '조선주']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14350</v>
+        <v>14330</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-0.69%</t>
+          <t>'-0.83%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.19</v>
       </c>
       <c r="E17" t="n">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="F17" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="G17" t="n">
-        <v>209</v>
+        <v>233</v>
       </c>
       <c r="H17" t="n">
         <v>9.83</v>
@@ -1990,7 +1990,7 @@
         <v>10.02</v>
       </c>
       <c r="O17" t="n">
-        <v>28759519845</v>
+        <v>31250544740</v>
       </c>
       <c r="P17" t="n">
         <v>40350</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>주가 하락 및 경영진에 대한 불만 표출. 공매도 및 연기금 매도 관련 부정적 언급.</t>
+          <t>대우건설, 신규 경영진에 대한 기대와 함께 주가 하락 및 공매도 관련 불만 표출.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['주가 하락', '공매도', '연기금']</t>
+          <t>['공매', '대차', '목표가']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>51900</v>
+        <v>52400</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.08%</t>
+          <t>'-1.13%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.03</v>
       </c>
       <c r="E18" t="n">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="F18" t="n">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="G18" t="n">
-        <v>739</v>
+        <v>779</v>
       </c>
       <c r="H18" t="n">
         <v>10.31</v>
@@ -2082,7 +2082,7 @@
         <v>10.34</v>
       </c>
       <c r="O18" t="n">
-        <v>43682132200</v>
+        <v>46089736750</v>
       </c>
       <c r="P18" t="n">
         <v>154800</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>코스피 강세에도 불구하고 주가 하락에 대한 불만 토로. 외인 매도세 및 악재 지속.</t>
+          <t>한화오션, 미 해군 상륙함 건조 제안서 제출 소식 및 코스피 지수 상승에 따른 반등 기대.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['공매도', '악재', '매도세']</t>
+          <t>['상륙함', '건조', '공매']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1986</v>
+        <v>1998</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-4.75%</t>
+          <t>'-4.17%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.39</v>
       </c>
       <c r="E19" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F19" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G19" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H19" t="n">
         <v>2.52</v>
@@ -2165,7 +2165,7 @@
         <v>2005</v>
       </c>
       <c r="L19" t="n">
-        <v>2010</v>
+        <v>2015</v>
       </c>
       <c r="M19" t="n">
         <v>1805</v>
@@ -2174,7 +2174,7 @@
         <v>2.13</v>
       </c>
       <c r="O19" t="n">
-        <v>11714635143</v>
+        <v>12248639426</v>
       </c>
       <c r="P19" t="n">
         <v>6190</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>액면병합 가격 대비 주가 하락에 대한 의문 제기. 공매도 및 대차 물량 증가 추정.</t>
+          <t>SK증권, 액면병합 가격 관련 문의 및 주가 하락에 대한 불만.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['액면병합', '공매도', '대차']</t>
+          <t>['액면병합', '공매', '전망']</t>
         </is>
       </c>
       <c r="X19" t="n">
